--- a/Population/BCIO-population-hierarchy.xlsx
+++ b/Population/BCIO-population-hierarchy.xlsx
@@ -577,7 +577,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:015795</t>
+          <t>BCIO:015798</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>mean value of valuable material resource owned population statistic</t>
+          <t>median value of valuable material resource owned population statistic</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>A(n) value of valuable material resource owned population statistic that is the mean value of value of valuable material resource owned in the population.</t>
+          <t>A(n) value of valuable material resource owned population statistic that is the median value of value of valuable material resource owned in the population.</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -4150,7 +4150,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:015798</t>
+          <t>BCIO:015795</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>median value of valuable material resource owned population statistic</t>
+          <t>mean value of valuable material resource owned population statistic</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>A(n) value of valuable material resource owned population statistic that is the median value of value of valuable material resource owned in the population.</t>
+          <t>A(n) value of valuable material resource owned population statistic that is the mean value of value of valuable material resource owned in the population.</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
@@ -7615,7 +7615,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BCIO:015591</t>
+          <t>BCIO:015657</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -7626,7 +7626,7 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>patient role population statistic</t>
+          <t>place of residence population statistic</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -7635,7 +7635,7 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>A population statistic about patient role.</t>
+          <t>A population statistic about place of residence.</t>
         </is>
       </c>
       <c r="P207" t="inlineStr"/>
@@ -7650,7 +7650,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BCIO:015465</t>
+          <t>BCIO:015659</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -7662,7 +7662,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>inpatient role population statistic</t>
+          <t>proportion place of residence population statistic</t>
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>A population statistic about inpatient role.</t>
+          <t>A(n) place of residence population statistic that is the proportion of people that have a place of residence in the population.</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -7685,7 +7685,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BCIO:015466</t>
+          <t>BCIO:015658</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -7695,17 +7695,17 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>percentage inpatient role population statistic</t>
-        </is>
-      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>percentage place of residence population statistic</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>A(n) inpatient role population statistic that is the percentage of people that have a inpatient role in the population.</t>
+          <t>A(n) place of residence population statistic that is the percentage of people that have a place of residence in the population.</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -7720,7 +7720,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BCIO:015467</t>
+          <t>BCIO:015591</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -7729,18 +7729,18 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>patient role population statistic</t>
+        </is>
+      </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>proportion inpatient role population statistic</t>
-        </is>
-      </c>
+      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>A(n) inpatient role population statistic that is the proportion of people that have a inpatient role in the population.</t>
+          <t>A population statistic about patient role.</t>
         </is>
       </c>
       <c r="P210" t="inlineStr"/>
@@ -7755,7 +7755,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BCIO:015593</t>
+          <t>BCIO:015465</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -7767,7 +7767,7 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>proportion patient role population statistic</t>
+          <t>inpatient role population statistic</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>A(n) patient role population statistic that is the proportion of people that have a patient role in the population.</t>
+          <t>A population statistic about inpatient role.</t>
         </is>
       </c>
       <c r="P211" t="inlineStr"/>
@@ -7790,7 +7790,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BCIO:015569</t>
+          <t>BCIO:015466</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -7800,17 +7800,17 @@
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>outpatient role population statistic</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>percentage inpatient role population statistic</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>A population statistic about outpatient role.</t>
+          <t>A(n) inpatient role population statistic that is the percentage of people that have a inpatient role in the population.</t>
         </is>
       </c>
       <c r="P212" t="inlineStr"/>
@@ -7825,7 +7825,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BCIO:015571</t>
+          <t>BCIO:015467</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -7838,14 +7838,14 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>proportion outpatient role population statistic</t>
+          <t>proportion inpatient role population statistic</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>A(n) outpatient role population statistic that is the proportion of people that have a outpatient role in the population.</t>
+          <t>A(n) inpatient role population statistic that is the proportion of people that have a inpatient role in the population.</t>
         </is>
       </c>
       <c r="P213" t="inlineStr"/>
@@ -7860,7 +7860,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BCIO:015570</t>
+          <t>BCIO:015593</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -7870,17 +7870,17 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>percentage outpatient role population statistic</t>
-        </is>
-      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>proportion patient role population statistic</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>A(n) outpatient role population statistic that is the percentage of people that have a outpatient role in the population.</t>
+          <t>A(n) patient role population statistic that is the proportion of people that have a patient role in the population.</t>
         </is>
       </c>
       <c r="P214" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BCIO:015592</t>
+          <t>BCIO:015569</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -7907,7 +7907,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>percentage patient role population statistic</t>
+          <t>outpatient role population statistic</t>
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
@@ -7915,7 +7915,7 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>A(n) patient role population statistic that is the percentage of people that have a patient role in the population.</t>
+          <t>A population statistic about outpatient role.</t>
         </is>
       </c>
       <c r="P215" t="inlineStr"/>
@@ -7930,7 +7930,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>BCIO:015657</t>
+          <t>BCIO:015571</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -7939,18 +7939,18 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>place of residence population statistic</t>
-        </is>
-      </c>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>proportion outpatient role population statistic</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>A population statistic about place of residence.</t>
+          <t>A(n) outpatient role population statistic that is the proportion of people that have a outpatient role in the population.</t>
         </is>
       </c>
       <c r="P216" t="inlineStr"/>
@@ -7965,7 +7965,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BCIO:015659</t>
+          <t>BCIO:015570</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -7975,17 +7975,17 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>proportion place of residence population statistic</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>percentage outpatient role population statistic</t>
+        </is>
+      </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>A(n) place of residence population statistic that is the proportion of people that have a place of residence in the population.</t>
+          <t>A(n) outpatient role population statistic that is the percentage of people that have a outpatient role in the population.</t>
         </is>
       </c>
       <c r="P217" t="inlineStr"/>
@@ -8000,7 +8000,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BCIO:015658</t>
+          <t>BCIO:015592</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -8012,7 +8012,7 @@
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
-          <t>percentage place of residence population statistic</t>
+          <t>percentage patient role population statistic</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
@@ -8020,7 +8020,7 @@
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>A(n) place of residence population statistic that is the percentage of people that have a place of residence in the population.</t>
+          <t>A(n) patient role population statistic that is the percentage of people that have a patient role in the population.</t>
         </is>
       </c>
       <c r="P218" t="inlineStr"/>
@@ -10345,7 +10345,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BCIO:015506</t>
+          <t>BCIO:015420</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -10356,7 +10356,7 @@
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
-          <t>member of a multi-person household population statistic</t>
+          <t>immigrant population statistic</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -10365,7 +10365,7 @@
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
-          <t>A population statistic about member of a multi-person household.</t>
+          <t>A population statistic about immigrant.</t>
         </is>
       </c>
       <c r="P285" t="inlineStr"/>
@@ -10380,7 +10380,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>BCIO:015515</t>
+          <t>BCIO:015421</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -10392,7 +10392,7 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
-          <t>member of a multi-person household some related population statistic</t>
+          <t>percentage immigrant population statistic</t>
         </is>
       </c>
       <c r="J286" t="inlineStr"/>
@@ -10400,7 +10400,7 @@
       <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
-          <t>A population statistic about member of a multi-person household some related.</t>
+          <t>A(n) immigrant population statistic that is the percentage of people that are a immigrant in the population.</t>
         </is>
       </c>
       <c r="P286" t="inlineStr"/>
@@ -10415,7 +10415,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>BCIO:015516</t>
+          <t>BCIO:015422</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -10425,17 +10425,17 @@
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>percentage member of a multi-person household some related population statistic</t>
-        </is>
-      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>proportion immigrant population statistic</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household some related population statistic that is the percentage of people that are a member of a multi-person household some related in the population.</t>
+          <t>A(n) immigrant population statistic that is the proportion of people that are a immigrant in the population.</t>
         </is>
       </c>
       <c r="P287" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BCIO:015517</t>
+          <t>BCIO:015506</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -10459,18 +10459,18 @@
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>member of a multi-person household population statistic</t>
+        </is>
+      </c>
       <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>proportion member of a multi-person household some related population statistic</t>
-        </is>
-      </c>
+      <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household some related population statistic that is the proportion of people that are a member of a multi-person household some related in the population.</t>
+          <t>A population statistic about member of a multi-person household.</t>
         </is>
       </c>
       <c r="P288" t="inlineStr"/>
@@ -10485,7 +10485,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>BCIO:015512</t>
+          <t>BCIO:015515</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -10497,7 +10497,7 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
-          <t>member of a multi-person household not related population statistic</t>
+          <t>member of a multi-person household some related population statistic</t>
         </is>
       </c>
       <c r="J289" t="inlineStr"/>
@@ -10505,7 +10505,7 @@
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
-          <t>A population statistic about member of a multi-person household not related.</t>
+          <t>A population statistic about member of a multi-person household some related.</t>
         </is>
       </c>
       <c r="P289" t="inlineStr"/>
@@ -10520,7 +10520,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BCIO:015513</t>
+          <t>BCIO:015516</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -10533,14 +10533,14 @@
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
-          <t>percentage member of a multi-person household not related population statistic</t>
+          <t>percentage member of a multi-person household some related population statistic</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household not related population statistic that is the percentage of people that are a member of a multi-person household not related in the population.</t>
+          <t>A(n) member of a multi-person household some related population statistic that is the percentage of people that are a member of a multi-person household some related in the population.</t>
         </is>
       </c>
       <c r="P290" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>BCIO:015514</t>
+          <t>BCIO:015517</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -10568,14 +10568,14 @@
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
-          <t>proportion member of a multi-person household not related population statistic</t>
+          <t>proportion member of a multi-person household some related population statistic</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household not related population statistic that is the proportion of people that are a member of a multi-person household not related in the population.</t>
+          <t>A(n) member of a multi-person household some related population statistic that is the proportion of people that are a member of a multi-person household some related in the population.</t>
         </is>
       </c>
       <c r="P291" t="inlineStr"/>
@@ -10590,7 +10590,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BCIO:015518</t>
+          <t>BCIO:015512</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -10602,7 +10602,7 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>member of a multi-person multi-generational household population statistic</t>
+          <t>member of a multi-person household not related population statistic</t>
         </is>
       </c>
       <c r="J292" t="inlineStr"/>
@@ -10610,7 +10610,7 @@
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
-          <t>A population statistic about member of a multi-person multi-generational household.</t>
+          <t>A population statistic about member of a multi-person household not related.</t>
         </is>
       </c>
       <c r="P292" t="inlineStr"/>
@@ -10625,7 +10625,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BCIO:015520</t>
+          <t>BCIO:015513</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>proportion member of a multi-person multi-generational household population statistic</t>
+          <t>percentage member of a multi-person household not related population statistic</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person multi-generational household population statistic that is the proportion of people that are a member of a multi-person multi-generational household in the population.</t>
+          <t>A(n) member of a multi-person household not related population statistic that is the percentage of people that are a member of a multi-person household not related in the population.</t>
         </is>
       </c>
       <c r="P293" t="inlineStr"/>
@@ -10660,7 +10660,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BCIO:015519</t>
+          <t>BCIO:015514</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -10673,14 +10673,14 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
-          <t>percentage member of a multi-person multi-generational household population statistic</t>
+          <t>proportion member of a multi-person household not related population statistic</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person multi-generational household population statistic that is the percentage of people that are a member of a multi-person multi-generational household in the population.</t>
+          <t>A(n) member of a multi-person household not related population statistic that is the proportion of people that are a member of a multi-person household not related in the population.</t>
         </is>
       </c>
       <c r="P294" t="inlineStr"/>
@@ -10695,7 +10695,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BCIO:015508</t>
+          <t>BCIO:015518</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -10707,7 +10707,7 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>proportion member of a multi-person household population statistic</t>
+          <t>member of a multi-person multi-generational household population statistic</t>
         </is>
       </c>
       <c r="J295" t="inlineStr"/>
@@ -10715,7 +10715,7 @@
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household population statistic that is the proportion of people that are a member of a multi-person household in the population.</t>
+          <t>A population statistic about member of a multi-person multi-generational household.</t>
         </is>
       </c>
       <c r="P295" t="inlineStr"/>
@@ -10730,7 +10730,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BCIO:015509</t>
+          <t>BCIO:015520</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -10740,17 +10740,17 @@
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>member of a multi-person household all related population statistic</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>proportion member of a multi-person multi-generational household population statistic</t>
+        </is>
+      </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
-          <t>A population statistic about member of a multi-person household all related.</t>
+          <t>A(n) member of a multi-person multi-generational household population statistic that is the proportion of people that are a member of a multi-person multi-generational household in the population.</t>
         </is>
       </c>
       <c r="P296" t="inlineStr"/>
@@ -10765,7 +10765,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>BCIO:015511</t>
+          <t>BCIO:015519</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -10778,14 +10778,14 @@
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
-          <t>proportion member of a multi-person household all related population statistic</t>
+          <t>percentage member of a multi-person multi-generational household population statistic</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household all related population statistic that is the proportion of people that are a member of a multi-person household all related in the population.</t>
+          <t>A(n) member of a multi-person multi-generational household population statistic that is the percentage of people that are a member of a multi-person multi-generational household in the population.</t>
         </is>
       </c>
       <c r="P297" t="inlineStr"/>
@@ -10800,7 +10800,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>BCIO:015510</t>
+          <t>BCIO:015508</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -10810,17 +10810,17 @@
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>percentage member of a multi-person household all related population statistic</t>
-        </is>
-      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>proportion member of a multi-person household population statistic</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household all related population statistic that is the percentage of people that are a member of a multi-person household all related in the population.</t>
+          <t>A(n) member of a multi-person household population statistic that is the proportion of people that are a member of a multi-person household in the population.</t>
         </is>
       </c>
       <c r="P298" t="inlineStr"/>
@@ -10835,7 +10835,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>BCIO:015507</t>
+          <t>BCIO:015509</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -10847,7 +10847,7 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>percentage member of a multi-person household population statistic</t>
+          <t>member of a multi-person household all related population statistic</t>
         </is>
       </c>
       <c r="J299" t="inlineStr"/>
@@ -10855,7 +10855,7 @@
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
-          <t>A(n) member of a multi-person household population statistic that is the percentage of people that are a member of a multi-person household in the population.</t>
+          <t>A population statistic about member of a multi-person household all related.</t>
         </is>
       </c>
       <c r="P299" t="inlineStr"/>
@@ -10870,7 +10870,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BCIO:015420</t>
+          <t>BCIO:015511</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -10879,18 +10879,18 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>immigrant population statistic</t>
-        </is>
-      </c>
+      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>proportion member of a multi-person household all related population statistic</t>
+        </is>
+      </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr">
         <is>
-          <t>A population statistic about immigrant.</t>
+          <t>A(n) member of a multi-person household all related population statistic that is the proportion of people that are a member of a multi-person household all related in the population.</t>
         </is>
       </c>
       <c r="P300" t="inlineStr"/>
@@ -10905,7 +10905,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BCIO:015421</t>
+          <t>BCIO:015510</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -10915,17 +10915,17 @@
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>percentage immigrant population statistic</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>percentage member of a multi-person household all related population statistic</t>
+        </is>
+      </c>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
-          <t>A(n) immigrant population statistic that is the percentage of people that are a immigrant in the population.</t>
+          <t>A(n) member of a multi-person household all related population statistic that is the percentage of people that are a member of a multi-person household all related in the population.</t>
         </is>
       </c>
       <c r="P301" t="inlineStr"/>
@@ -10940,7 +10940,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BCIO:015422</t>
+          <t>BCIO:015507</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -10952,7 +10952,7 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>proportion immigrant population statistic</t>
+          <t>percentage member of a multi-person household population statistic</t>
         </is>
       </c>
       <c r="J302" t="inlineStr"/>
@@ -10960,7 +10960,7 @@
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
-          <t>A(n) immigrant population statistic that is the proportion of people that are a immigrant in the population.</t>
+          <t>A(n) member of a multi-person household population statistic that is the percentage of people that are a member of a multi-person household in the population.</t>
         </is>
       </c>
       <c r="P302" t="inlineStr"/>
@@ -12445,7 +12445,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>BCIO:015711</t>
+          <t>BCIO:015402</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -12456,7 +12456,7 @@
       <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
-          <t>second generation immigrant population statistic</t>
+          <t>homemaker status population statistic</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -12465,7 +12465,7 @@
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr">
         <is>
-          <t>A population statistic about second generation immigrant.</t>
+          <t>A population statistic about homemaker status.</t>
         </is>
       </c>
       <c r="P345" t="inlineStr"/>
@@ -12480,7 +12480,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>BCIO:015712</t>
+          <t>BCIO:015404</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -12492,7 +12492,7 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
-          <t>percentage second generation immigrant population statistic</t>
+          <t>proportion homemaker status population statistic</t>
         </is>
       </c>
       <c r="J346" t="inlineStr"/>
@@ -12500,7 +12500,7 @@
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr">
         <is>
-          <t>A(n) second generation immigrant population statistic that is the percentage of people that are a second generation immigrant in the population.</t>
+          <t>A(n) homemaker status population statistic that is the proportion of people that have a homemaker status in the population.</t>
         </is>
       </c>
       <c r="P346" t="inlineStr"/>
@@ -12515,7 +12515,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BCIO:015713</t>
+          <t>BCIO:015403</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
-          <t>proportion second generation immigrant population statistic</t>
+          <t>percentage homemaker status population statistic</t>
         </is>
       </c>
       <c r="J347" t="inlineStr"/>
@@ -12535,7 +12535,7 @@
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
-          <t>A(n) second generation immigrant population statistic that is the proportion of people that are a second generation immigrant in the population.</t>
+          <t>A(n) homemaker status population statistic that is the percentage of people that have a homemaker status in the population.</t>
         </is>
       </c>
       <c r="P347" t="inlineStr"/>
@@ -12550,7 +12550,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>BCIO:015402</t>
+          <t>BCIO:015711</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -12561,7 +12561,7 @@
       <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
-          <t>homemaker status population statistic</t>
+          <t>second generation immigrant population statistic</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
@@ -12570,7 +12570,7 @@
       <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr">
         <is>
-          <t>A population statistic about homemaker status.</t>
+          <t>A population statistic about second generation immigrant.</t>
         </is>
       </c>
       <c r="P348" t="inlineStr"/>
@@ -12585,7 +12585,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BCIO:015404</t>
+          <t>BCIO:015712</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
-          <t>proportion homemaker status population statistic</t>
+          <t>percentage second generation immigrant population statistic</t>
         </is>
       </c>
       <c r="J349" t="inlineStr"/>
@@ -12605,7 +12605,7 @@
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr">
         <is>
-          <t>A(n) homemaker status population statistic that is the proportion of people that have a homemaker status in the population.</t>
+          <t>A(n) second generation immigrant population statistic that is the percentage of people that are a second generation immigrant in the population.</t>
         </is>
       </c>
       <c r="P349" t="inlineStr"/>
@@ -12620,7 +12620,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BCIO:015403</t>
+          <t>BCIO:015713</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -12632,7 +12632,7 @@
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
-          <t>percentage homemaker status population statistic</t>
+          <t>proportion second generation immigrant population statistic</t>
         </is>
       </c>
       <c r="J350" t="inlineStr"/>
@@ -12640,7 +12640,7 @@
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr">
         <is>
-          <t>A(n) homemaker status population statistic that is the percentage of people that have a homemaker status in the population.</t>
+          <t>A(n) second generation immigrant population statistic that is the proportion of people that are a second generation immigrant in the population.</t>
         </is>
       </c>
       <c r="P350" t="inlineStr"/>
@@ -13705,7 +13705,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>BCIO:015687</t>
+          <t>BCIO:015881</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
-          <t>religious group membership population statistic</t>
+          <t>monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="I381" t="inlineStr"/>
@@ -13725,7 +13725,7 @@
       <c r="L381" t="inlineStr"/>
       <c r="M381" t="inlineStr">
         <is>
-          <t>A population statistic about religious group membership.</t>
+          <t>A population statistic about monetary human income data item.</t>
         </is>
       </c>
       <c r="P381" t="inlineStr"/>
@@ -13740,7 +13740,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>BCIO:015688</t>
+          <t>BCIO:015883</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -13752,7 +13752,7 @@
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr">
         <is>
-          <t>percentage religious group membership population statistic</t>
+          <t>minimum monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="J382" t="inlineStr"/>
@@ -13760,7 +13760,7 @@
       <c r="L382" t="inlineStr"/>
       <c r="M382" t="inlineStr">
         <is>
-          <t>A(n) religious group membership population statistic that is the percentage of people that have a religious group membership in the population.</t>
+          <t>A(n) monetary human income data item population statistic that is the minimum value of monetary human income data item in the population.</t>
         </is>
       </c>
       <c r="P382" t="inlineStr"/>
@@ -13775,7 +13775,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>BCIO:015689</t>
+          <t>BCIO:015885</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -13787,7 +13787,7 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr">
         <is>
-          <t>proportion religious group membership population statistic</t>
+          <t>median monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="J383" t="inlineStr"/>
@@ -13795,7 +13795,7 @@
       <c r="L383" t="inlineStr"/>
       <c r="M383" t="inlineStr">
         <is>
-          <t>A(n) religious group membership population statistic that is the proportion of people that have a religious group membership in the population.</t>
+          <t>A(n) monetary human income data item population statistic that is the median value of monetary human income data item in the population.</t>
         </is>
       </c>
       <c r="P383" t="inlineStr"/>
@@ -13810,7 +13810,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>BCIO:015690</t>
+          <t>BCIO:015867</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -13819,18 +13819,18 @@
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>rent-free occupier population statistic</t>
-        </is>
-      </c>
-      <c r="I384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>household income population statistic</t>
+        </is>
+      </c>
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr">
         <is>
-          <t>A population statistic about rent-free occupier.</t>
+          <t>A population statistic about household income.</t>
         </is>
       </c>
       <c r="P384" t="inlineStr"/>
@@ -13845,7 +13845,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>BCIO:015222</t>
+          <t>BCIO:015872</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -13855,17 +13855,17 @@
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>agreed rent-free occupier population statistic</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>percentage household income population statistic</t>
+        </is>
+      </c>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
       <c r="M385" t="inlineStr">
         <is>
-          <t>A population statistic about agreed rent-free occupier.</t>
+          <t>A(n) household income population statistic that is the percentage value of household income in the population.</t>
         </is>
       </c>
       <c r="P385" t="inlineStr"/>
@@ -13880,7 +13880,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>BCIO:015224</t>
+          <t>BCIO:015870</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -13893,14 +13893,14 @@
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr">
         <is>
-          <t>proportion agreed rent-free occupier population statistic</t>
+          <t>maximum household income population statistic</t>
         </is>
       </c>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr">
         <is>
-          <t>A(n) agreed rent-free occupier population statistic that is the proportion of people that are a agreed rent-free occupier in the population.</t>
+          <t>A(n) household income population statistic that is the maximum value of household income in the population.</t>
         </is>
       </c>
       <c r="P386" t="inlineStr"/>
@@ -13915,7 +13915,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>BCIO:015223</t>
+          <t>BCIO:015873</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -13928,14 +13928,14 @@
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr">
         <is>
-          <t>percentage agreed rent-free occupier population statistic</t>
+          <t>proportion household income population statistic</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
       <c r="M387" t="inlineStr">
         <is>
-          <t>A(n) agreed rent-free occupier population statistic that is the percentage of people that are a agreed rent-free occupier in the population.</t>
+          <t>A(n) household income population statistic that is the proportion of individuals having a household income in the population.</t>
         </is>
       </c>
       <c r="P387" t="inlineStr"/>
@@ -13950,7 +13950,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>BCIO:015693</t>
+          <t>BCIO:015869</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -13960,17 +13960,17 @@
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>rent-free occupier without owner's permission population statistic</t>
-        </is>
-      </c>
-      <c r="J388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>minimum household income population statistic</t>
+        </is>
+      </c>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
       <c r="M388" t="inlineStr">
         <is>
-          <t>A population statistic about rent-free occupier without owner's permission.</t>
+          <t>A(n) household income population statistic that is the minimum value of household income in the population.</t>
         </is>
       </c>
       <c r="P388" t="inlineStr"/>
@@ -13985,7 +13985,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>BCIO:015695</t>
+          <t>BCIO:015871</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -13998,14 +13998,14 @@
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
-          <t>proportion rent-free occupier without owner's permission population statistic</t>
+          <t>median household income population statistic</t>
         </is>
       </c>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
       <c r="M389" t="inlineStr">
         <is>
-          <t>A(n) rent-free occupier without owner's permission population statistic that is the proportion of people that are a rent-free occupier without owner's permission in the population.</t>
+          <t>A(n) household income population statistic that is the median value of household income in the population.</t>
         </is>
       </c>
       <c r="P389" t="inlineStr"/>
@@ -14020,7 +14020,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>BCIO:015694</t>
+          <t>BCIO:015868</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -14033,14 +14033,14 @@
       <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr">
         <is>
-          <t>percentage rent-free occupier without owner's permission population statistic</t>
+          <t>mean household income population statistic</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
       <c r="M390" t="inlineStr">
         <is>
-          <t>A(n) rent-free occupier without owner's permission population statistic that is the percentage of people that are a rent-free occupier without owner's permission in the population.</t>
+          <t>A(n) household income population statistic that is the mean value of household income in the population.</t>
         </is>
       </c>
       <c r="P390" t="inlineStr"/>
@@ -14055,7 +14055,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>BCIO:015692</t>
+          <t>BCIO:015882</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -14067,7 +14067,7 @@
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
-          <t>proportion rent-free occupier population statistic</t>
+          <t>mean monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="J391" t="inlineStr"/>
@@ -14075,7 +14075,7 @@
       <c r="L391" t="inlineStr"/>
       <c r="M391" t="inlineStr">
         <is>
-          <t>A(n) rent-free occupier population statistic that is the proportion of people that are a rent-free occupier in the population.</t>
+          <t>A(n) monetary human income data item population statistic that is the mean value of monetary human income data item in the population.</t>
         </is>
       </c>
       <c r="P391" t="inlineStr"/>
@@ -14090,7 +14090,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>BCIO:015691</t>
+          <t>BCIO:015886</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr">
         <is>
-          <t>percentage rent-free occupier population statistic</t>
+          <t>percentage monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="J392" t="inlineStr"/>
@@ -14110,7 +14110,7 @@
       <c r="L392" t="inlineStr"/>
       <c r="M392" t="inlineStr">
         <is>
-          <t>A(n) rent-free occupier population statistic that is the percentage of people that are a rent-free occupier in the population.</t>
+          <t>A(n) monetary human income data item population statistic that is the percentage value of monetary human income data item in the population.</t>
         </is>
       </c>
       <c r="P392" t="inlineStr"/>
@@ -14125,7 +14125,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>BCIO:015315</t>
+          <t>BCIO:015874</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -14134,18 +14134,18 @@
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>ethnic group membership population statistic</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr"/>
       <c r="M393" t="inlineStr">
         <is>
-          <t>A population statistic about ethnic group membership.</t>
+          <t>A population statistic about individual person income data item.</t>
         </is>
       </c>
       <c r="P393" t="inlineStr"/>
@@ -14160,7 +14160,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>BCIO:015316</t>
+          <t>BCIO:015880</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -14170,17 +14170,17 @@
       <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>percentage ethnic group membership population statistic</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>proportion individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr"/>
       <c r="M394" t="inlineStr">
         <is>
-          <t>A(n) ethnic group membership population statistic that is the percentage of people that have a ethnic group membership in the population.</t>
+          <t>A(n) individual person income data item population statistic that is the proportion of individuals having a individual person income data item in the population.</t>
         </is>
       </c>
       <c r="P394" t="inlineStr"/>
@@ -14195,7 +14195,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>BCIO:015317</t>
+          <t>BCIO:015878</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -14205,17 +14205,17 @@
       <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr">
-        <is>
-          <t>proportion ethnic group membership population statistic</t>
-        </is>
-      </c>
-      <c r="J395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>median individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr"/>
       <c r="M395" t="inlineStr">
         <is>
-          <t>A(n) ethnic group membership population statistic that is the proportion of people that have a ethnic group membership in the population.</t>
+          <t>A(n) individual person income data item population statistic that is the median value of individual person income data item in the population.</t>
         </is>
       </c>
       <c r="P395" t="inlineStr"/>
@@ -14230,7 +14230,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>BCIO:015393</t>
+          <t>BCIO:015875</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -14239,18 +14239,18 @@
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr"/>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
+      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>mean individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr"/>
       <c r="M396" t="inlineStr">
         <is>
-          <t>A population statistic about history of exposure to an occupational hazard.</t>
+          <t>A(n) individual person income data item population statistic that is the mean value of individual person income data item in the population.</t>
         </is>
       </c>
       <c r="P396" t="inlineStr"/>
@@ -14265,7 +14265,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>BCIO:015395</t>
+          <t>BCIO:015877</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -14275,17 +14275,17 @@
       <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>proportion history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
-      <c r="J397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>maximum individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
       <c r="M397" t="inlineStr">
         <is>
-          <t>A(n) history of exposure to an occupational hazard population statistic that is the proportion of people that have a history of exposure to an occupational hazard in the population.</t>
+          <t>A(n) individual person income data item population statistic that is the maximum value of individual person income data item in the population.</t>
         </is>
       </c>
       <c r="P397" t="inlineStr"/>
@@ -14300,7 +14300,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>BCIO:015394</t>
+          <t>BCIO:015879</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -14310,17 +14310,17 @@
       <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>percentage history of exposure to an occupational hazard population statistic</t>
-        </is>
-      </c>
-      <c r="J398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>percentage individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
       <c r="M398" t="inlineStr">
         <is>
-          <t>A(n) history of exposure to an occupational hazard population statistic that is the percentage of people that have a history of exposure to an occupational hazard in the population.</t>
+          <t>A(n) individual person income data item population statistic that is the percentage value of individual person income data item in the population.</t>
         </is>
       </c>
       <c r="P398" t="inlineStr"/>
@@ -14335,7 +14335,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>BCIO:015524</t>
+          <t>BCIO:015876</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -14344,18 +14344,18 @@
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>mental capability population statistic</t>
-        </is>
-      </c>
+      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>minimum individual person income data item population statistic</t>
+        </is>
+      </c>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
       <c r="M399" t="inlineStr">
         <is>
-          <t>A population statistic about mental capability.</t>
+          <t>A(n) individual person income data item population statistic that is the minimum value of individual person income data item in the population.</t>
         </is>
       </c>
       <c r="P399" t="inlineStr"/>
@@ -14370,7 +14370,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>BCIO:015525</t>
+          <t>BCIO:015887</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -14382,7 +14382,7 @@
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
-          <t>mean mental capability population statistic</t>
+          <t>proportion monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="J400" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       <c r="L400" t="inlineStr"/>
       <c r="M400" t="inlineStr">
         <is>
-          <t>A(n) mental capability population statistic that is the mean value of mental capability in the population.</t>
+          <t>A(n) monetary human income data item population statistic that is the proportion of individuals having a monetary human income data item in the population.</t>
         </is>
       </c>
       <c r="P400" t="inlineStr"/>
@@ -14405,7 +14405,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>BCIO:015528</t>
+          <t>BCIO:015884</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -14417,7 +14417,7 @@
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr">
         <is>
-          <t>median mental capability population statistic</t>
+          <t>maximum monetary human income data item population statistic</t>
         </is>
       </c>
       <c r="J401" t="inlineStr"/>
@@ -14425,7 +14425,7 @@
       <c r="L401" t="inlineStr"/>
       <c r="M401" t="inlineStr">
         <is>
-          <t>A(n) mental capability population statistic that is the median value of mental capability in the population.</t>
+          <t>A(n) monetary human income data item population statistic that is the maximum value of monetary human income data item in the population.</t>
         </is>
       </c>
       <c r="P401" t="inlineStr"/>
@@ -14440,7 +14440,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>BCIO:015527</t>
+          <t>BCIO:015860</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -14452,7 +14452,7 @@
       <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
-          <t>maximum mental capability population statistic</t>
+          <t>government assistance income data item population statistic</t>
         </is>
       </c>
       <c r="J402" t="inlineStr"/>
@@ -14460,7 +14460,7 @@
       <c r="L402" t="inlineStr"/>
       <c r="M402" t="inlineStr">
         <is>
-          <t>A(n) mental capability population statistic that is the maximum value of mental capability in the population.</t>
+          <t>A population statistic about government assistance income data item.</t>
         </is>
       </c>
       <c r="P402" t="inlineStr"/>
@@ -14475,7 +14475,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>BCIO:015526</t>
+          <t>BCIO:015861</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -14485,17 +14485,17 @@
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>minimum mental capability population statistic</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>mean government assistance income data item population statistic</t>
+        </is>
+      </c>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
       <c r="M403" t="inlineStr">
         <is>
-          <t>A(n) mental capability population statistic that is the minimum value of mental capability in the population.</t>
+          <t>A(n) government assistance income data item population statistic that is the mean value of government assistance income data item in the population.</t>
         </is>
       </c>
       <c r="P403" t="inlineStr"/>
@@ -14510,7 +14510,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>BCIO:015529</t>
+          <t>BCIO:015865</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -14520,17 +14520,17 @@
       <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>percentage mental capability population statistic</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>percentage government assistance income data item population statistic</t>
+        </is>
+      </c>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
       <c r="M404" t="inlineStr">
         <is>
-          <t>A(n) mental capability population statistic that is the percentage value of mental capability in the population.</t>
+          <t>A(n) government assistance income data item population statistic that is the percentage value of government assistance income data item in the population.</t>
         </is>
       </c>
       <c r="P404" t="inlineStr"/>
@@ -14545,7 +14545,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>BCIO:015484</t>
+          <t>BCIO:015863</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -14555,17 +14555,17 @@
       <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>linguistic capability population statistic</t>
-        </is>
-      </c>
-      <c r="J405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>maximum government assistance income data item population statistic</t>
+        </is>
+      </c>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
       <c r="M405" t="inlineStr">
         <is>
-          <t>A population statistic about linguistic capability.</t>
+          <t>A(n) government assistance income data item population statistic that is the maximum value of government assistance income data item in the population.</t>
         </is>
       </c>
       <c r="P405" t="inlineStr"/>
@@ -14580,7 +14580,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>BCIO:015489</t>
+          <t>BCIO:015864</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -14593,14 +14593,14 @@
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr">
         <is>
-          <t>percentage linguistic capability population statistic</t>
+          <t>median government assistance income data item population statistic</t>
         </is>
       </c>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
       <c r="M406" t="inlineStr">
         <is>
-          <t>A(n) linguistic capability population statistic that is the percentage value of linguistic capability in the population.</t>
+          <t>A(n) government assistance income data item population statistic that is the median value of government assistance income data item in the population.</t>
         </is>
       </c>
       <c r="P406" t="inlineStr"/>
@@ -14615,7 +14615,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>BCIO:015487</t>
+          <t>BCIO:015862</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -14628,14 +14628,14 @@
       <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr">
         <is>
-          <t>maximum linguistic capability population statistic</t>
+          <t>minimum government assistance income data item population statistic</t>
         </is>
       </c>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr"/>
       <c r="M407" t="inlineStr">
         <is>
-          <t>A(n) linguistic capability population statistic that is the maximum value of linguistic capability in the population.</t>
+          <t>A(n) government assistance income data item population statistic that is the minimum value of government assistance income data item in the population.</t>
         </is>
       </c>
       <c r="P407" t="inlineStr"/>
@@ -14650,7 +14650,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>BCIO:015168</t>
+          <t>BCIO:015866</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -14663,14 +14663,14 @@
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr">
         <is>
-          <t>ability to write in intervention language population statistic</t>
+          <t>proportion government assistance income data item population statistic</t>
         </is>
       </c>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr"/>
       <c r="M408" t="inlineStr">
         <is>
-          <t>A population statistic about ability to write in intervention language.</t>
+          <t>A(n) government assistance income data item population statistic that is the proportion of individuals having a government assistance income data item in the population.</t>
         </is>
       </c>
       <c r="P408" t="inlineStr"/>
@@ -14685,7 +14685,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>BCIO:015170</t>
+          <t>BCIO:015687</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -14694,18 +14694,18 @@
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>religious group membership population statistic</t>
+        </is>
+      </c>
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>proportion ability to write in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr">
         <is>
-          <t>A(n) ability to write in intervention language population statistic that is the proportion of people that have a ability to write in intervention language in the population.</t>
+          <t>A population statistic about religious group membership.</t>
         </is>
       </c>
       <c r="P409" t="inlineStr"/>
@@ -14720,7 +14720,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>BCIO:015169</t>
+          <t>BCIO:015688</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -14730,17 +14730,17 @@
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>percentage religious group membership population statistic</t>
+        </is>
+      </c>
       <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>percentage ability to write in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr"/>
       <c r="M410" t="inlineStr">
         <is>
-          <t>A(n) ability to write in intervention language population statistic that is the percentage of people that have a ability to write in intervention language in the population.</t>
+          <t>A(n) religious group membership population statistic that is the percentage of people that have a religious group membership in the population.</t>
         </is>
       </c>
       <c r="P410" t="inlineStr"/>
@@ -14755,7 +14755,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>BCIO:015100</t>
+          <t>BCIO:015689</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -14765,17 +14765,17 @@
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>ability to read in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>proportion religious group membership population statistic</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr"/>
       <c r="M411" t="inlineStr">
         <is>
-          <t>A population statistic about ability to read in intervention language.</t>
+          <t>A(n) religious group membership population statistic that is the proportion of people that have a religious group membership in the population.</t>
         </is>
       </c>
       <c r="P411" t="inlineStr"/>
@@ -14790,7 +14790,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>BCIO:015164</t>
+          <t>BCIO:015690</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -14799,18 +14799,18 @@
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>rent-free occupier population statistic</t>
+        </is>
+      </c>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>proportion ability to read in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr">
         <is>
-          <t>A(n) ability to read in intervention language population statistic that is the proportion of people that have a ability to read in intervention language in the population.</t>
+          <t>A population statistic about rent-free occupier.</t>
         </is>
       </c>
       <c r="P412" t="inlineStr"/>
@@ -14825,7 +14825,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>BCIO:015109</t>
+          <t>BCIO:015222</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -14835,17 +14835,17 @@
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>agreed rent-free occupier population statistic</t>
+        </is>
+      </c>
       <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr">
-        <is>
-          <t>percentage ability to read in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
       <c r="M413" t="inlineStr">
         <is>
-          <t>A(n) ability to read in intervention language population statistic that is the percentage of people that have a ability to read in intervention language in the population.</t>
+          <t>A population statistic about agreed rent-free occupier.</t>
         </is>
       </c>
       <c r="P413" t="inlineStr"/>
@@ -14860,7 +14860,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>BCIO:015485</t>
+          <t>BCIO:015224</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -14873,14 +14873,14 @@
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr">
         <is>
-          <t>mean linguistic capability population statistic</t>
+          <t>proportion agreed rent-free occupier population statistic</t>
         </is>
       </c>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
       <c r="M414" t="inlineStr">
         <is>
-          <t>A(n) linguistic capability population statistic that is the mean value of linguistic capability in the population.</t>
+          <t>A(n) agreed rent-free occupier population statistic that is the proportion of people that are a agreed rent-free occupier in the population.</t>
         </is>
       </c>
       <c r="P414" t="inlineStr"/>
@@ -14895,7 +14895,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>BCIO:015081</t>
+          <t>BCIO:015223</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -14908,14 +14908,14 @@
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr">
         <is>
-          <t>ability to comprehend spoken intervention language population statistic</t>
+          <t>percentage agreed rent-free occupier population statistic</t>
         </is>
       </c>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr"/>
       <c r="M415" t="inlineStr">
         <is>
-          <t>A population statistic about ability to comprehend spoken intervention language.</t>
+          <t>A(n) agreed rent-free occupier population statistic that is the percentage of people that are a agreed rent-free occupier in the population.</t>
         </is>
       </c>
       <c r="P415" t="inlineStr"/>
@@ -14930,7 +14930,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>BCIO:015082</t>
+          <t>BCIO:015693</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -14940,17 +14940,17 @@
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr"/>
-      <c r="I416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>rent-free occupier without owner's permission population statistic</t>
+        </is>
+      </c>
       <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>percentage ability to comprehend spoken intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr"/>
       <c r="M416" t="inlineStr">
         <is>
-          <t>A(n) ability to comprehend spoken intervention language population statistic that is the percentage of people that have a ability to comprehend spoken intervention language in the population.</t>
+          <t>A population statistic about rent-free occupier without owner's permission.</t>
         </is>
       </c>
       <c r="P416" t="inlineStr"/>
@@ -14965,7 +14965,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>BCIO:015099</t>
+          <t>BCIO:015695</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -14976,16 +14976,16 @@
       <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>proportion ability to comprehend spoken intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>proportion rent-free occupier without owner's permission population statistic</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr"/>
       <c r="M417" t="inlineStr">
         <is>
-          <t>A(n) ability to comprehend spoken intervention language population statistic that is the proportion of people that have a ability to comprehend spoken intervention language in the population.</t>
+          <t>A(n) rent-free occupier without owner's permission population statistic that is the proportion of people that are a rent-free occupier without owner's permission in the population.</t>
         </is>
       </c>
       <c r="P417" t="inlineStr"/>
@@ -15000,7 +15000,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>BCIO:015488</t>
+          <t>BCIO:015694</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -15013,14 +15013,14 @@
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr">
         <is>
-          <t>median linguistic capability population statistic</t>
+          <t>percentage rent-free occupier without owner's permission population statistic</t>
         </is>
       </c>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr"/>
       <c r="M418" t="inlineStr">
         <is>
-          <t>A(n) linguistic capability population statistic that is the median value of linguistic capability in the population.</t>
+          <t>A(n) rent-free occupier without owner's permission population statistic that is the percentage of people that are a rent-free occupier without owner's permission in the population.</t>
         </is>
       </c>
       <c r="P418" t="inlineStr"/>
@@ -15035,7 +15035,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>BCIO:015477</t>
+          <t>BCIO:015692</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -15045,17 +15045,17 @@
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>proportion rent-free occupier population statistic</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr"/>
       <c r="M419" t="inlineStr">
         <is>
-          <t>A population statistic about language proficiency.</t>
+          <t>A(n) rent-free occupier population statistic that is the proportion of people that are a rent-free occupier in the population.</t>
         </is>
       </c>
       <c r="P419" t="inlineStr"/>
@@ -15070,7 +15070,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>BCIO:015483</t>
+          <t>BCIO:015691</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -15080,17 +15080,17 @@
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>percentage rent-free occupier population statistic</t>
+        </is>
+      </c>
       <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>proportion language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr"/>
       <c r="M420" t="inlineStr">
         <is>
-          <t>A(n) language proficiency population statistic that is the proportion of individuals having a language proficiency in the population.</t>
+          <t>A(n) rent-free occupier population statistic that is the percentage of people that are a rent-free occupier in the population.</t>
         </is>
       </c>
       <c r="P420" t="inlineStr"/>
@@ -15105,7 +15105,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>BCIO:015480</t>
+          <t>BCIO:015315</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -15114,18 +15114,18 @@
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>ethnic group membership population statistic</t>
+        </is>
+      </c>
       <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>maximum language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
       <c r="M421" t="inlineStr">
         <is>
-          <t>A(n) language proficiency population statistic that is the maximum value of language proficiency in the population.</t>
+          <t>A population statistic about ethnic group membership.</t>
         </is>
       </c>
       <c r="P421" t="inlineStr"/>
@@ -15140,7 +15140,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>BCIO:015482</t>
+          <t>BCIO:015316</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -15150,17 +15150,17 @@
       <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr"/>
-      <c r="I422" t="inlineStr"/>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>percentage ethnic group membership population statistic</t>
+        </is>
+      </c>
       <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>percentage language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr"/>
       <c r="M422" t="inlineStr">
         <is>
-          <t>A(n) language proficiency population statistic that is the percentage value of language proficiency in the population.</t>
+          <t>A(n) ethnic group membership population statistic that is the percentage of people that have a ethnic group membership in the population.</t>
         </is>
       </c>
       <c r="P422" t="inlineStr"/>
@@ -15175,7 +15175,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>BCIO:015481</t>
+          <t>BCIO:015317</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -15185,17 +15185,17 @@
       <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr"/>
-      <c r="I423" t="inlineStr"/>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>proportion ethnic group membership population statistic</t>
+        </is>
+      </c>
       <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>median language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr"/>
       <c r="M423" t="inlineStr">
         <is>
-          <t>A(n) language proficiency population statistic that is the median value of language proficiency in the population.</t>
+          <t>A(n) ethnic group membership population statistic that is the proportion of people that have a ethnic group membership in the population.</t>
         </is>
       </c>
       <c r="P423" t="inlineStr"/>
@@ -15210,7 +15210,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BCIO:015479</t>
+          <t>BCIO:015393</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -15219,18 +15219,18 @@
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr">
-        <is>
-          <t>minimum language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr"/>
       <c r="M424" t="inlineStr">
         <is>
-          <t>A(n) language proficiency population statistic that is the minimum value of language proficiency in the population.</t>
+          <t>A population statistic about history of exposure to an occupational hazard.</t>
         </is>
       </c>
       <c r="P424" t="inlineStr"/>
@@ -15245,7 +15245,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>BCIO:015478</t>
+          <t>BCIO:015395</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -15255,17 +15255,17 @@
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>proportion history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
       <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr">
-        <is>
-          <t>mean language proficiency population statistic</t>
-        </is>
-      </c>
+      <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
       <c r="M425" t="inlineStr">
         <is>
-          <t>A(n) language proficiency population statistic that is the mean value of language proficiency in the population.</t>
+          <t>A(n) history of exposure to an occupational hazard population statistic that is the proportion of people that have a history of exposure to an occupational hazard in the population.</t>
         </is>
       </c>
       <c r="P425" t="inlineStr"/>
@@ -15280,7 +15280,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>BCIO:015486</t>
+          <t>BCIO:015394</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -15290,17 +15290,17 @@
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>minimum linguistic capability population statistic</t>
-        </is>
-      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>percentage history of exposure to an occupational hazard population statistic</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
       <c r="M426" t="inlineStr">
         <is>
-          <t>A(n) linguistic capability population statistic that is the minimum value of linguistic capability in the population.</t>
+          <t>A(n) history of exposure to an occupational hazard population statistic that is the percentage of people that have a history of exposure to an occupational hazard in the population.</t>
         </is>
       </c>
       <c r="P426" t="inlineStr"/>
@@ -15315,7 +15315,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>BCIO:015165</t>
+          <t>BCIO:015524</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -15324,18 +15324,18 @@
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>mental capability population statistic</t>
+        </is>
+      </c>
       <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>ability to speak in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr"/>
       <c r="M427" t="inlineStr">
         <is>
-          <t>A population statistic about ability to speak in intervention language.</t>
+          <t>A population statistic about mental capability.</t>
         </is>
       </c>
       <c r="P427" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>BCIO:015167</t>
+          <t>BCIO:015525</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -15360,17 +15360,17 @@
       <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr"/>
-      <c r="I428" t="inlineStr"/>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>mean mental capability population statistic</t>
+        </is>
+      </c>
       <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>proportion ability to speak in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
       <c r="M428" t="inlineStr">
         <is>
-          <t>A(n) ability to speak in intervention language population statistic that is the proportion of people that have a ability to speak in intervention language in the population.</t>
+          <t>A(n) mental capability population statistic that is the mean value of mental capability in the population.</t>
         </is>
       </c>
       <c r="P428" t="inlineStr"/>
@@ -15385,7 +15385,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>BCIO:015166</t>
+          <t>BCIO:015528</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -15395,17 +15395,17 @@
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>median mental capability population statistic</t>
+        </is>
+      </c>
       <c r="J429" t="inlineStr"/>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>percentage ability to speak in intervention language population statistic</t>
-        </is>
-      </c>
+      <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
       <c r="M429" t="inlineStr">
         <is>
-          <t>A(n) ability to speak in intervention language population statistic that is the percentage of people that have a ability to speak in intervention language in the population.</t>
+          <t>A(n) mental capability population statistic that is the median value of mental capability in the population.</t>
         </is>
       </c>
       <c r="P429" t="inlineStr"/>
@@ -15420,7 +15420,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>BCIO:015490</t>
+          <t>BCIO:015527</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -15430,17 +15430,17 @@
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
-      <c r="I430" t="inlineStr"/>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>proportion linguistic capability population statistic</t>
-        </is>
-      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>maximum mental capability population statistic</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr"/>
       <c r="M430" t="inlineStr">
         <is>
-          <t>A(n) linguistic capability population statistic that is the proportion of individuals having a linguistic capability in the population.</t>
+          <t>A(n) mental capability population statistic that is the maximum value of mental capability in the population.</t>
         </is>
       </c>
       <c r="P430" t="inlineStr"/>
@@ -15455,7 +15455,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BCIO:015530</t>
+          <t>BCIO:015526</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -15467,7 +15467,7 @@
       <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr">
         <is>
-          <t>proportion mental capability population statistic</t>
+          <t>minimum mental capability population statistic</t>
         </is>
       </c>
       <c r="J431" t="inlineStr"/>
@@ -15475,7 +15475,7 @@
       <c r="L431" t="inlineStr"/>
       <c r="M431" t="inlineStr">
         <is>
-          <t>A(n) mental capability population statistic that is the proportion of individuals having a mental capability in the population.</t>
+          <t>A(n) mental capability population statistic that is the minimum value of mental capability in the population.</t>
         </is>
       </c>
       <c r="P431" t="inlineStr"/>
@@ -15490,7 +15490,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>BCIO:015264</t>
+          <t>BCIO:015529</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -15499,18 +15499,18 @@
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr"/>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>caregiving role population statistic</t>
-        </is>
-      </c>
-      <c r="I432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>percentage mental capability population statistic</t>
+        </is>
+      </c>
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr"/>
       <c r="M432" t="inlineStr">
         <is>
-          <t>A population statistic about caregiving role.</t>
+          <t>A(n) mental capability population statistic that is the percentage value of mental capability in the population.</t>
         </is>
       </c>
       <c r="P432" t="inlineStr"/>
@@ -15525,7 +15525,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>BCIO:015265</t>
+          <t>BCIO:015484</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -15537,7 +15537,7 @@
       <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr">
         <is>
-          <t>percentage caregiving role population statistic</t>
+          <t>linguistic capability population statistic</t>
         </is>
       </c>
       <c r="J433" t="inlineStr"/>
@@ -15545,7 +15545,7 @@
       <c r="L433" t="inlineStr"/>
       <c r="M433" t="inlineStr">
         <is>
-          <t>A(n) caregiving role population statistic that is the percentage of people that have a caregiving role in the population.</t>
+          <t>A population statistic about linguistic capability.</t>
         </is>
       </c>
       <c r="P433" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>BCIO:015266</t>
+          <t>BCIO:015489</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -15570,17 +15570,17 @@
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>proportion caregiving role population statistic</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>percentage linguistic capability population statistic</t>
+        </is>
+      </c>
       <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr">
         <is>
-          <t>A(n) caregiving role population statistic that is the proportion of people that have a caregiving role in the population.</t>
+          <t>A(n) linguistic capability population statistic that is the percentage value of linguistic capability in the population.</t>
         </is>
       </c>
       <c r="P434" t="inlineStr"/>
@@ -15595,7 +15595,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>BCIO:015643</t>
+          <t>BCIO:015487</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -15604,18 +15604,18 @@
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>personal vulnerability population statistic</t>
-        </is>
-      </c>
+      <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr"/>
-      <c r="J435" t="inlineStr"/>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>maximum linguistic capability population statistic</t>
+        </is>
+      </c>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr">
         <is>
-          <t>A population statistic about personal vulnerability.</t>
+          <t>A(n) linguistic capability population statistic that is the maximum value of linguistic capability in the population.</t>
         </is>
       </c>
       <c r="P435" t="inlineStr"/>
@@ -15630,7 +15630,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>BCIO:015646</t>
+          <t>BCIO:015168</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -15640,17 +15640,17 @@
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>maximum personal vulnerability population statistic</t>
-        </is>
-      </c>
-      <c r="J436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>ability to write in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the maximum value of personal vulnerability in the population.</t>
+          <t>A population statistic about ability to write in intervention language.</t>
         </is>
       </c>
       <c r="P436" t="inlineStr"/>
@@ -15665,7 +15665,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>BCIO:015645</t>
+          <t>BCIO:015170</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -15675,17 +15675,17 @@
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>minimum personal vulnerability population statistic</t>
-        </is>
-      </c>
+      <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr"/>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>proportion ability to write in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr"/>
       <c r="M437" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the minimum value of personal vulnerability in the population.</t>
+          <t>A(n) ability to write in intervention language population statistic that is the proportion of people that have a ability to write in intervention language in the population.</t>
         </is>
       </c>
       <c r="P437" t="inlineStr"/>
@@ -15700,7 +15700,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>BCIO:015644</t>
+          <t>BCIO:015169</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -15710,17 +15710,17 @@
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>mean personal vulnerability population statistic</t>
-        </is>
-      </c>
+      <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>percentage ability to write in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the mean value of personal vulnerability in the population.</t>
+          <t>A(n) ability to write in intervention language population statistic that is the percentage of people that have a ability to write in intervention language in the population.</t>
         </is>
       </c>
       <c r="P438" t="inlineStr"/>
@@ -15735,7 +15735,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>BCIO:015650</t>
+          <t>BCIO:015100</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -15745,17 +15745,17 @@
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>personal vulnerability to harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="J439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>ability to read in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
         <is>
-          <t>A population statistic about personal vulnerability to harmful behaviour.</t>
+          <t>A population statistic about ability to read in intervention language.</t>
         </is>
       </c>
       <c r="P439" t="inlineStr"/>
@@ -15770,7 +15770,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>BCIO:015652</t>
+          <t>BCIO:015164</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -15781,16 +15781,16 @@
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>minimum personal vulnerability to harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>proportion ability to read in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the minimum value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) ability to read in intervention language population statistic that is the proportion of people that have a ability to read in intervention language in the population.</t>
         </is>
       </c>
       <c r="P440" t="inlineStr"/>
@@ -15805,7 +15805,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>BCIO:015656</t>
+          <t>BCIO:015109</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -15816,16 +15816,16 @@
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>proportion personal vulnerability to harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>percentage ability to read in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the proportion of individuals having a personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) ability to read in intervention language population statistic that is the percentage of people that have a ability to read in intervention language in the population.</t>
         </is>
       </c>
       <c r="P441" t="inlineStr"/>
@@ -15840,7 +15840,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>BCIO:015653</t>
+          <t>BCIO:015485</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -15853,14 +15853,14 @@
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr">
         <is>
-          <t>maximum personal vulnerability to harmful behaviour population statistic</t>
+          <t>mean linguistic capability population statistic</t>
         </is>
       </c>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the maximum value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) linguistic capability population statistic that is the mean value of linguistic capability in the population.</t>
         </is>
       </c>
       <c r="P442" t="inlineStr"/>
@@ -15875,7 +15875,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>BCIO:015654</t>
+          <t>BCIO:015081</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -15888,14 +15888,14 @@
       <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr">
         <is>
-          <t>median personal vulnerability to harmful behaviour population statistic</t>
+          <t>ability to comprehend spoken intervention language population statistic</t>
         </is>
       </c>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the median value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A population statistic about ability to comprehend spoken intervention language.</t>
         </is>
       </c>
       <c r="P443" t="inlineStr"/>
@@ -15910,7 +15910,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>BCIO:015651</t>
+          <t>BCIO:015082</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -15921,16 +15921,16 @@
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>mean personal vulnerability to harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>percentage ability to comprehend spoken intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the mean value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) ability to comprehend spoken intervention language population statistic that is the percentage of people that have a ability to comprehend spoken intervention language in the population.</t>
         </is>
       </c>
       <c r="P444" t="inlineStr"/>
@@ -15945,7 +15945,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>BCIO:015655</t>
+          <t>BCIO:015099</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -15956,16 +15956,16 @@
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>percentage personal vulnerability to harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>proportion ability to comprehend spoken intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr"/>
       <c r="M445" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the percentage value of personal vulnerability to harmful behaviour in the population.</t>
+          <t>A(n) ability to comprehend spoken intervention language population statistic that is the proportion of people that have a ability to comprehend spoken intervention language in the population.</t>
         </is>
       </c>
       <c r="P445" t="inlineStr"/>
@@ -15980,7 +15980,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>BCIO:015647</t>
+          <t>BCIO:015488</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -15990,17 +15990,17 @@
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>median personal vulnerability population statistic</t>
-        </is>
-      </c>
-      <c r="J446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>median linguistic capability population statistic</t>
+        </is>
+      </c>
       <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the median value of personal vulnerability in the population.</t>
+          <t>A(n) linguistic capability population statistic that is the median value of linguistic capability in the population.</t>
         </is>
       </c>
       <c r="P446" t="inlineStr"/>
@@ -16015,7 +16015,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>BCIO:015648</t>
+          <t>BCIO:015477</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -16025,17 +16025,17 @@
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>percentage personal vulnerability population statistic</t>
-        </is>
-      </c>
-      <c r="J447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the percentage value of personal vulnerability in the population.</t>
+          <t>A population statistic about language proficiency.</t>
         </is>
       </c>
       <c r="P447" t="inlineStr"/>
@@ -16050,7 +16050,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>BCIO:015649</t>
+          <t>BCIO:015483</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -16060,17 +16060,17 @@
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>proportion personal vulnerability population statistic</t>
-        </is>
-      </c>
+      <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>proportion language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr">
         <is>
-          <t>A(n) personal vulnerability population statistic that is the proportion of individuals having a personal vulnerability in the population.</t>
+          <t>A(n) language proficiency population statistic that is the proportion of individuals having a language proficiency in the population.</t>
         </is>
       </c>
       <c r="P448" t="inlineStr"/>
@@ -16085,7 +16085,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>BCIO:015540</t>
+          <t>BCIO:015480</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -16094,18 +16094,18 @@
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>non-gendered identity population statistic</t>
-        </is>
-      </c>
+      <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>maximum language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>A population statistic about non-gendered identity.</t>
+          <t>A(n) language proficiency population statistic that is the maximum value of language proficiency in the population.</t>
         </is>
       </c>
       <c r="P449" t="inlineStr"/>
@@ -16120,7 +16120,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>BCIO:015541</t>
+          <t>BCIO:015482</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -16130,17 +16130,17 @@
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>percentage non-gendered identity population statistic</t>
-        </is>
-      </c>
+      <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>percentage language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr"/>
       <c r="M450" t="inlineStr">
         <is>
-          <t>A(n) non-gendered identity population statistic that is the percentage of people that have a non-gendered identity in the population.</t>
+          <t>A(n) language proficiency population statistic that is the percentage value of language proficiency in the population.</t>
         </is>
       </c>
       <c r="P450" t="inlineStr"/>
@@ -16155,7 +16155,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>BCIO:015542</t>
+          <t>BCIO:015481</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -16165,17 +16165,17 @@
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>proportion non-gendered identity population statistic</t>
-        </is>
-      </c>
+      <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>median language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
         <is>
-          <t>A(n) non-gendered identity population statistic that is the proportion of people that have a non-gendered identity in the population.</t>
+          <t>A(n) language proficiency population statistic that is the median value of language proficiency in the population.</t>
         </is>
       </c>
       <c r="P451" t="inlineStr"/>
@@ -16190,7 +16190,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>BCIO:015857</t>
+          <t>BCIO:015479</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -16199,18 +16199,18 @@
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>leadership role population statistic</t>
-        </is>
-      </c>
+      <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr"/>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>minimum language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
-          <t>A population statistic about leadership role.</t>
+          <t>A(n) language proficiency population statistic that is the minimum value of language proficiency in the population.</t>
         </is>
       </c>
       <c r="P452" t="inlineStr"/>
@@ -16225,7 +16225,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>BCIO:015858</t>
+          <t>BCIO:015478</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -16235,17 +16235,17 @@
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>percentage leadership role population statistic</t>
-        </is>
-      </c>
+      <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr"/>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>mean language proficiency population statistic</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr">
         <is>
-          <t>A(n) leadership role population statistic that is the percentage of people that have a leadership role in the population.</t>
+          <t>A(n) language proficiency population statistic that is the mean value of language proficiency in the population.</t>
         </is>
       </c>
       <c r="P453" t="inlineStr"/>
@@ -16260,7 +16260,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>BCIO:015859</t>
+          <t>BCIO:015486</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -16270,17 +16270,17 @@
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>proportion leadership role population statistic</t>
-        </is>
-      </c>
-      <c r="J454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>minimum linguistic capability population statistic</t>
+        </is>
+      </c>
       <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
         <is>
-          <t>A(n) leadership role population statistic that is the proportion of people that have a leadership role in the population.</t>
+          <t>A(n) linguistic capability population statistic that is the minimum value of linguistic capability in the population.</t>
         </is>
       </c>
       <c r="P454" t="inlineStr"/>
@@ -16295,7 +16295,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>BCIO:015560</t>
+          <t>BCIO:015165</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -16304,18 +16304,18 @@
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>occupier of employer-provided housing population statistic</t>
-        </is>
-      </c>
+      <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
-      <c r="J455" t="inlineStr"/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>ability to speak in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
       <c r="M455" t="inlineStr">
         <is>
-          <t>A population statistic about occupier of employer-provided housing.</t>
+          <t>A population statistic about ability to speak in intervention language.</t>
         </is>
       </c>
       <c r="P455" t="inlineStr"/>
@@ -16330,7 +16330,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BCIO:015561</t>
+          <t>BCIO:015167</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -16340,17 +16340,17 @@
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>percentage occupier of employer-provided housing population statistic</t>
-        </is>
-      </c>
+      <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>proportion ability to speak in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr"/>
       <c r="M456" t="inlineStr">
         <is>
-          <t>A(n) occupier of employer-provided housing population statistic that is the percentage of people that are a occupier of employer-provided housing in the population.</t>
+          <t>A(n) ability to speak in intervention language population statistic that is the proportion of people that have a ability to speak in intervention language in the population.</t>
         </is>
       </c>
       <c r="P456" t="inlineStr"/>
@@ -16365,7 +16365,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BCIO:015562</t>
+          <t>BCIO:015166</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -16375,17 +16375,17 @@
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>proportion occupier of employer-provided housing population statistic</t>
-        </is>
-      </c>
+      <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>percentage ability to speak in intervention language population statistic</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr">
         <is>
-          <t>A(n) occupier of employer-provided housing population statistic that is the proportion of people that are a occupier of employer-provided housing in the population.</t>
+          <t>A(n) ability to speak in intervention language population statistic that is the percentage of people that have a ability to speak in intervention language in the population.</t>
         </is>
       </c>
       <c r="P457" t="inlineStr"/>
@@ -16400,7 +16400,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>BCIO:015594</t>
+          <t>BCIO:015490</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -16409,18 +16409,18 @@
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr"/>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>personal history of behavioural lapse population statistic</t>
-        </is>
-      </c>
+      <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>proportion linguistic capability population statistic</t>
+        </is>
+      </c>
       <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr">
         <is>
-          <t>A population statistic about personal history of behavioural lapse.</t>
+          <t>A(n) linguistic capability population statistic that is the proportion of individuals having a linguistic capability in the population.</t>
         </is>
       </c>
       <c r="P458" t="inlineStr"/>
@@ -16435,7 +16435,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>BCIO:015595</t>
+          <t>BCIO:015530</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -16447,7 +16447,7 @@
       <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr">
         <is>
-          <t>mean personal history of behavioural lapse population statistic</t>
+          <t>proportion mental capability population statistic</t>
         </is>
       </c>
       <c r="J459" t="inlineStr"/>
@@ -16455,7 +16455,7 @@
       <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the mean value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) mental capability population statistic that is the proportion of individuals having a mental capability in the population.</t>
         </is>
       </c>
       <c r="P459" t="inlineStr"/>
@@ -16470,7 +16470,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>BCIO:015598</t>
+          <t>BCIO:015264</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -16479,18 +16479,18 @@
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr"/>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr">
-        <is>
-          <t>median personal history of behavioural lapse population statistic</t>
-        </is>
-      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>caregiving role population statistic</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the median value of personal history of behavioural lapse in the population.</t>
+          <t>A population statistic about caregiving role.</t>
         </is>
       </c>
       <c r="P460" t="inlineStr"/>
@@ -16505,7 +16505,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>BCIO:015597</t>
+          <t>BCIO:015265</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -16517,7 +16517,7 @@
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr">
         <is>
-          <t>maximum personal history of behavioural lapse population statistic</t>
+          <t>percentage caregiving role population statistic</t>
         </is>
       </c>
       <c r="J461" t="inlineStr"/>
@@ -16525,7 +16525,7 @@
       <c r="L461" t="inlineStr"/>
       <c r="M461" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the maximum value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) caregiving role population statistic that is the percentage of people that have a caregiving role in the population.</t>
         </is>
       </c>
       <c r="P461" t="inlineStr"/>
@@ -16540,7 +16540,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>BCIO:015596</t>
+          <t>BCIO:015266</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -16552,7 +16552,7 @@
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr">
         <is>
-          <t>minimum personal history of behavioural lapse population statistic</t>
+          <t>proportion caregiving role population statistic</t>
         </is>
       </c>
       <c r="J462" t="inlineStr"/>
@@ -16560,7 +16560,7 @@
       <c r="L462" t="inlineStr"/>
       <c r="M462" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the minimum value of personal history of behavioural lapse in the population.</t>
+          <t>A(n) caregiving role population statistic that is the proportion of people that have a caregiving role in the population.</t>
         </is>
       </c>
       <c r="P462" t="inlineStr"/>
@@ -16575,7 +16575,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>BCIO:015599</t>
+          <t>BCIO:015643</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -16584,18 +16584,18 @@
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr">
-        <is>
-          <t>percentage personal history of behavioural lapse population statistic</t>
-        </is>
-      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>personal vulnerability population statistic</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr"/>
       <c r="M463" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the percentage value of personal history of behavioural lapse in the population.</t>
+          <t>A population statistic about personal vulnerability.</t>
         </is>
       </c>
       <c r="P463" t="inlineStr"/>
@@ -16610,7 +16610,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BCIO:015600</t>
+          <t>BCIO:015646</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -16622,7 +16622,7 @@
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr">
         <is>
-          <t>proportion personal history of behavioural lapse population statistic</t>
+          <t>maximum personal vulnerability population statistic</t>
         </is>
       </c>
       <c r="J464" t="inlineStr"/>
@@ -16630,7 +16630,7 @@
       <c r="L464" t="inlineStr"/>
       <c r="M464" t="inlineStr">
         <is>
-          <t>A(n) personal history of behavioural lapse population statistic that is the proportion of individuals having a personal history of behavioural lapse in the population.</t>
+          <t>A(n) personal vulnerability population statistic that is the maximum value of personal vulnerability in the population.</t>
         </is>
       </c>
       <c r="P464" t="inlineStr"/>
@@ -16645,7 +16645,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>BCIO:015279</t>
+          <t>BCIO:015645</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -16654,18 +16654,18 @@
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>country of birth population statistic</t>
-        </is>
-      </c>
-      <c r="I465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>minimum personal vulnerability population statistic</t>
+        </is>
+      </c>
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
         <is>
-          <t>A population statistic about country of birth.</t>
+          <t>A(n) personal vulnerability population statistic that is the minimum value of personal vulnerability in the population.</t>
         </is>
       </c>
       <c r="P465" t="inlineStr"/>
@@ -16680,7 +16680,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>BCIO:015280</t>
+          <t>BCIO:015644</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -16692,7 +16692,7 @@
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr">
         <is>
-          <t>percentage country of birth population statistic</t>
+          <t>mean personal vulnerability population statistic</t>
         </is>
       </c>
       <c r="J466" t="inlineStr"/>
@@ -16700,7 +16700,7 @@
       <c r="L466" t="inlineStr"/>
       <c r="M466" t="inlineStr">
         <is>
-          <t>A(n) country of birth population statistic that is the percentage of people that have a country of birth in the population.</t>
+          <t>A(n) personal vulnerability population statistic that is the mean value of personal vulnerability in the population.</t>
         </is>
       </c>
       <c r="P466" t="inlineStr"/>
@@ -16715,7 +16715,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>BCIO:015281</t>
+          <t>BCIO:015650</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -16727,7 +16727,7 @@
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr">
         <is>
-          <t>proportion country of birth population statistic</t>
+          <t>personal vulnerability to harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="J467" t="inlineStr"/>
@@ -16735,7 +16735,7 @@
       <c r="L467" t="inlineStr"/>
       <c r="M467" t="inlineStr">
         <is>
-          <t>A(n) country of birth population statistic that is the proportion of people that have a country of birth in the population.</t>
+          <t>A population statistic about personal vulnerability to harmful behaviour.</t>
         </is>
       </c>
       <c r="P467" t="inlineStr"/>
@@ -16750,7 +16750,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>BCIO:015666</t>
+          <t>BCIO:015652</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -16759,18 +16759,18 @@
       <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>protective factor for harmful behaviour population statistic</t>
-        </is>
-      </c>
+      <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
-      <c r="J468" t="inlineStr"/>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>minimum personal vulnerability to harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr">
         <is>
-          <t>A population statistic about protective factor for harmful behaviour.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the minimum value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P468" t="inlineStr"/>
@@ -16785,7 +16785,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BCIO:015671</t>
+          <t>BCIO:015656</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -16795,17 +16795,17 @@
       <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr">
-        <is>
-          <t>percentage protective factor for harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="J469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>proportion personal vulnerability to harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
       <c r="M469" t="inlineStr">
         <is>
-          <t>A(n) protective factor for harmful behaviour population statistic that is the percentage value of protective factor for harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the proportion of individuals having a personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P469" t="inlineStr"/>
@@ -16820,7 +16820,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>BCIO:015672</t>
+          <t>BCIO:015653</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -16830,17 +16830,17 @@
       <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr">
-        <is>
-          <t>proportion protective factor for harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="J470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>maximum personal vulnerability to harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr">
         <is>
-          <t>A(n) protective factor for harmful behaviour population statistic that is the proportion of individuals having a protective factor for harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the maximum value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P470" t="inlineStr"/>
@@ -16855,7 +16855,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>BCIO:015670</t>
+          <t>BCIO:015654</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -16865,17 +16865,17 @@
       <c r="F471" t="inlineStr"/>
       <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr">
-        <is>
-          <t>median protective factor for harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="J471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>median personal vulnerability to harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr"/>
       <c r="M471" t="inlineStr">
         <is>
-          <t>A(n) protective factor for harmful behaviour population statistic that is the median value of protective factor for harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the median value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P471" t="inlineStr"/>
@@ -16890,7 +16890,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>BCIO:015667</t>
+          <t>BCIO:015651</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -16900,17 +16900,17 @@
       <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr"/>
-      <c r="I472" t="inlineStr">
-        <is>
-          <t>mean protective factor for harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="J472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>mean personal vulnerability to harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr"/>
       <c r="M472" t="inlineStr">
         <is>
-          <t>A(n) protective factor for harmful behaviour population statistic that is the mean value of protective factor for harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the mean value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P472" t="inlineStr"/>
@@ -16925,7 +16925,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BCIO:015668</t>
+          <t>BCIO:015655</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -16935,17 +16935,17 @@
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr">
-        <is>
-          <t>minimum protective factor for harmful behaviour population statistic</t>
-        </is>
-      </c>
-      <c r="J473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>percentage personal vulnerability to harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr"/>
       <c r="M473" t="inlineStr">
         <is>
-          <t>A(n) protective factor for harmful behaviour population statistic that is the minimum value of protective factor for harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability to harmful behaviour population statistic that is the percentage value of personal vulnerability to harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P473" t="inlineStr"/>
@@ -16960,7 +16960,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BCIO:015669</t>
+          <t>BCIO:015647</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -16972,7 +16972,7 @@
       <c r="H474" t="inlineStr"/>
       <c r="I474" t="inlineStr">
         <is>
-          <t>maximum protective factor for harmful behaviour population statistic</t>
+          <t>median personal vulnerability population statistic</t>
         </is>
       </c>
       <c r="J474" t="inlineStr"/>
@@ -16980,7 +16980,7 @@
       <c r="L474" t="inlineStr"/>
       <c r="M474" t="inlineStr">
         <is>
-          <t>A(n) protective factor for harmful behaviour population statistic that is the maximum value of protective factor for harmful behaviour in the population.</t>
+          <t>A(n) personal vulnerability population statistic that is the median value of personal vulnerability in the population.</t>
         </is>
       </c>
       <c r="P474" t="inlineStr"/>
@@ -16995,7 +16995,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>BCIO:015270</t>
+          <t>BCIO:015648</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -17004,18 +17004,18 @@
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr"/>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>child population statistic</t>
-        </is>
-      </c>
-      <c r="I475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>percentage personal vulnerability population statistic</t>
+        </is>
+      </c>
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr"/>
       <c r="M475" t="inlineStr">
         <is>
-          <t>A population statistic about child.</t>
+          <t>A(n) personal vulnerability population statistic that is the percentage value of personal vulnerability in the population.</t>
         </is>
       </c>
       <c r="P475" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>BCIO:015272</t>
+          <t>BCIO:015649</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -17042,7 +17042,7 @@
       <c r="H476" t="inlineStr"/>
       <c r="I476" t="inlineStr">
         <is>
-          <t>proportion child population statistic</t>
+          <t>proportion personal vulnerability population statistic</t>
         </is>
       </c>
       <c r="J476" t="inlineStr"/>
@@ -17050,7 +17050,7 @@
       <c r="L476" t="inlineStr"/>
       <c r="M476" t="inlineStr">
         <is>
-          <t>A(n) child population statistic that is the proportion of people that are a child in the population.</t>
+          <t>A(n) personal vulnerability population statistic that is the proportion of individuals having a personal vulnerability in the population.</t>
         </is>
       </c>
       <c r="P476" t="inlineStr"/>
@@ -17065,7 +17065,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>BCIO:015271</t>
+          <t>BCIO:015540</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -17074,18 +17074,18 @@
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr">
-        <is>
-          <t>percentage child population statistic</t>
-        </is>
-      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>non-gendered identity population statistic</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr"/>
       <c r="M477" t="inlineStr">
         <is>
-          <t>A(n) child population statistic that is the percentage of people that are a child in the population.</t>
+          <t>A population statistic about non-gendered identity.</t>
         </is>
       </c>
       <c r="P477" t="inlineStr"/>
@@ -17100,7 +17100,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>BCIO:015881</t>
+          <t>BCIO:015541</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -17109,18 +17109,18 @@
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>monetary human income data item population statistic</t>
-        </is>
-      </c>
-      <c r="I478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>percentage non-gendered identity population statistic</t>
+        </is>
+      </c>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr"/>
       <c r="M478" t="inlineStr">
         <is>
-          <t>A population statistic about monetary human income data item.</t>
+          <t>A(n) non-gendered identity population statistic that is the percentage of people that have a non-gendered identity in the population.</t>
         </is>
       </c>
       <c r="P478" t="inlineStr"/>
@@ -17135,7 +17135,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>BCIO:015883</t>
+          <t>BCIO:015542</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -17147,7 +17147,7 @@
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr">
         <is>
-          <t>minimum monetary human income data item population statistic</t>
+          <t>proportion non-gendered identity population statistic</t>
         </is>
       </c>
       <c r="J479" t="inlineStr"/>
@@ -17155,7 +17155,7 @@
       <c r="L479" t="inlineStr"/>
       <c r="M479" t="inlineStr">
         <is>
-          <t>A(n) monetary human income data item population statistic that is the minimum value of monetary human income data item in the population.</t>
+          <t>A(n) non-gendered identity population statistic that is the proportion of people that have a non-gendered identity in the population.</t>
         </is>
       </c>
       <c r="P479" t="inlineStr"/>
@@ -17170,7 +17170,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>BCIO:015885</t>
+          <t>BCIO:015857</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -17179,18 +17179,18 @@
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
-      <c r="I480" t="inlineStr">
-        <is>
-          <t>median monetary human income data item population statistic</t>
-        </is>
-      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>leadership role population statistic</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr">
         <is>
-          <t>A(n) monetary human income data item population statistic that is the median value of monetary human income data item in the population.</t>
+          <t>A population statistic about leadership role.</t>
         </is>
       </c>
       <c r="P480" t="inlineStr"/>
@@ -17205,7 +17205,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>BCIO:015867</t>
+          <t>BCIO:015858</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -17217,7 +17217,7 @@
       <c r="H481" t="inlineStr"/>
       <c r="I481" t="inlineStr">
         <is>
-          <t>household income population statistic</t>
+          <t>percentage leadership role population statistic</t>
         </is>
       </c>
       <c r="J481" t="inlineStr"/>
@@ -17225,7 +17225,7 @@
       <c r="L481" t="inlineStr"/>
       <c r="M481" t="inlineStr">
         <is>
-          <t>A population statistic about household income.</t>
+          <t>A(n) leadership role population statistic that is the percentage of people that have a leadership role in the population.</t>
         </is>
       </c>
       <c r="P481" t="inlineStr"/>
@@ -17240,7 +17240,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>BCIO:015872</t>
+          <t>BCIO:015859</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -17250,17 +17250,17 @@
       <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr">
-        <is>
-          <t>percentage household income population statistic</t>
-        </is>
-      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>proportion leadership role population statistic</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the percentage value of household income in the population.</t>
+          <t>A(n) leadership role population statistic that is the proportion of people that have a leadership role in the population.</t>
         </is>
       </c>
       <c r="P482" t="inlineStr"/>
@@ -17275,7 +17275,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>BCIO:015870</t>
+          <t>BCIO:015560</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -17284,18 +17284,18 @@
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>occupier of employer-provided housing population statistic</t>
+        </is>
+      </c>
       <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr">
-        <is>
-          <t>maximum household income population statistic</t>
-        </is>
-      </c>
+      <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr"/>
       <c r="M483" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the maximum value of household income in the population.</t>
+          <t>A population statistic about occupier of employer-provided housing.</t>
         </is>
       </c>
       <c r="P483" t="inlineStr"/>
@@ -17310,7 +17310,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>BCIO:015873</t>
+          <t>BCIO:015561</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -17320,17 +17320,17 @@
       <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr">
-        <is>
-          <t>proportion household income population statistic</t>
-        </is>
-      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>percentage occupier of employer-provided housing population statistic</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr"/>
       <c r="M484" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the proportion of individuals having a household income in the population.</t>
+          <t>A(n) occupier of employer-provided housing population statistic that is the percentage of people that are a occupier of employer-provided housing in the population.</t>
         </is>
       </c>
       <c r="P484" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>BCIO:015869</t>
+          <t>BCIO:015562</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -17355,17 +17355,17 @@
       <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr"/>
       <c r="H485" t="inlineStr"/>
-      <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr">
-        <is>
-          <t>minimum household income population statistic</t>
-        </is>
-      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>proportion occupier of employer-provided housing population statistic</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr"/>
       <c r="M485" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the minimum value of household income in the population.</t>
+          <t>A(n) occupier of employer-provided housing population statistic that is the proportion of people that are a occupier of employer-provided housing in the population.</t>
         </is>
       </c>
       <c r="P485" t="inlineStr"/>
@@ -17380,7 +17380,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>BCIO:015871</t>
+          <t>BCIO:015279</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -17389,18 +17389,18 @@
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>country of birth population statistic</t>
+        </is>
+      </c>
       <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr">
-        <is>
-          <t>median household income population statistic</t>
-        </is>
-      </c>
+      <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr"/>
       <c r="M486" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the median value of household income in the population.</t>
+          <t>A population statistic about country of birth.</t>
         </is>
       </c>
       <c r="P486" t="inlineStr"/>
@@ -17415,7 +17415,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BCIO:015868</t>
+          <t>BCIO:015280</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -17425,17 +17425,17 @@
       <c r="F487" t="inlineStr"/>
       <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr">
-        <is>
-          <t>mean household income population statistic</t>
-        </is>
-      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>percentage country of birth population statistic</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr"/>
       <c r="M487" t="inlineStr">
         <is>
-          <t>A(n) household income population statistic that is the mean value of household income in the population.</t>
+          <t>A(n) country of birth population statistic that is the percentage of people that have a country of birth in the population.</t>
         </is>
       </c>
       <c r="P487" t="inlineStr"/>
@@ -17450,7 +17450,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>BCIO:015882</t>
+          <t>BCIO:015281</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr">
         <is>
-          <t>mean monetary human income data item population statistic</t>
+          <t>proportion country of birth population statistic</t>
         </is>
       </c>
       <c r="J488" t="inlineStr"/>
@@ -17470,7 +17470,7 @@
       <c r="L488" t="inlineStr"/>
       <c r="M488" t="inlineStr">
         <is>
-          <t>A(n) monetary human income data item population statistic that is the mean value of monetary human income data item in the population.</t>
+          <t>A(n) country of birth population statistic that is the proportion of people that have a country of birth in the population.</t>
         </is>
       </c>
       <c r="P488" t="inlineStr"/>
@@ -17485,7 +17485,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>BCIO:015886</t>
+          <t>BCIO:015594</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -17494,18 +17494,18 @@
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr"/>
-      <c r="H489" t="inlineStr"/>
-      <c r="I489" t="inlineStr">
-        <is>
-          <t>percentage monetary human income data item population statistic</t>
-        </is>
-      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>personal history of behavioural lapse population statistic</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr">
         <is>
-          <t>A(n) monetary human income data item population statistic that is the percentage value of monetary human income data item in the population.</t>
+          <t>A population statistic about personal history of behavioural lapse.</t>
         </is>
       </c>
       <c r="P489" t="inlineStr"/>
@@ -17520,7 +17520,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>BCIO:015874</t>
+          <t>BCIO:015595</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -17532,7 +17532,7 @@
       <c r="H490" t="inlineStr"/>
       <c r="I490" t="inlineStr">
         <is>
-          <t>individual person income data item population statistic</t>
+          <t>mean personal history of behavioural lapse population statistic</t>
         </is>
       </c>
       <c r="J490" t="inlineStr"/>
@@ -17540,7 +17540,7 @@
       <c r="L490" t="inlineStr"/>
       <c r="M490" t="inlineStr">
         <is>
-          <t>A population statistic about individual person income data item.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the mean value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
       <c r="P490" t="inlineStr"/>
@@ -17555,7 +17555,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>BCIO:015880</t>
+          <t>BCIO:015598</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -17565,17 +17565,17 @@
       <c r="F491" t="inlineStr"/>
       <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr"/>
-      <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr">
-        <is>
-          <t>proportion individual person income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>median personal history of behavioural lapse population statistic</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr"/>
       <c r="M491" t="inlineStr">
         <is>
-          <t>A(n) individual person income data item population statistic that is the proportion of individuals having a individual person income data item in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the median value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
       <c r="P491" t="inlineStr"/>
@@ -17590,7 +17590,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>BCIO:015878</t>
+          <t>BCIO:015597</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -17600,17 +17600,17 @@
       <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr"/>
-      <c r="I492" t="inlineStr"/>
-      <c r="J492" t="inlineStr">
-        <is>
-          <t>median individual person income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>maximum personal history of behavioural lapse population statistic</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr"/>
       <c r="M492" t="inlineStr">
         <is>
-          <t>A(n) individual person income data item population statistic that is the median value of individual person income data item in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the maximum value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
       <c r="P492" t="inlineStr"/>
@@ -17625,7 +17625,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>BCIO:015875</t>
+          <t>BCIO:015596</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -17635,17 +17635,17 @@
       <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr"/>
-      <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr">
-        <is>
-          <t>mean individual person income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>minimum personal history of behavioural lapse population statistic</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr"/>
       <c r="M493" t="inlineStr">
         <is>
-          <t>A(n) individual person income data item population statistic that is the mean value of individual person income data item in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the minimum value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
       <c r="P493" t="inlineStr"/>
@@ -17660,7 +17660,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BCIO:015877</t>
+          <t>BCIO:015599</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -17670,17 +17670,17 @@
       <c r="F494" t="inlineStr"/>
       <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr">
-        <is>
-          <t>maximum individual person income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>percentage personal history of behavioural lapse population statistic</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr"/>
       <c r="M494" t="inlineStr">
         <is>
-          <t>A(n) individual person income data item population statistic that is the maximum value of individual person income data item in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the percentage value of personal history of behavioural lapse in the population.</t>
         </is>
       </c>
       <c r="P494" t="inlineStr"/>
@@ -17695,7 +17695,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>BCIO:015879</t>
+          <t>BCIO:015600</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -17705,17 +17705,17 @@
       <c r="F495" t="inlineStr"/>
       <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
-      <c r="J495" t="inlineStr">
-        <is>
-          <t>percentage individual person income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>proportion personal history of behavioural lapse population statistic</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr"/>
       <c r="M495" t="inlineStr">
         <is>
-          <t>A(n) individual person income data item population statistic that is the percentage value of individual person income data item in the population.</t>
+          <t>A(n) personal history of behavioural lapse population statistic that is the proportion of individuals having a personal history of behavioural lapse in the population.</t>
         </is>
       </c>
       <c r="P495" t="inlineStr"/>
@@ -17730,7 +17730,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BCIO:015876</t>
+          <t>BCIO:015666</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -17739,18 +17739,18 @@
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>protective factor for harmful behaviour population statistic</t>
+        </is>
+      </c>
       <c r="I496" t="inlineStr"/>
-      <c r="J496" t="inlineStr">
-        <is>
-          <t>minimum individual person income data item population statistic</t>
-        </is>
-      </c>
+      <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr">
         <is>
-          <t>A(n) individual person income data item population statistic that is the minimum value of individual person income data item in the population.</t>
+          <t>A population statistic about protective factor for harmful behaviour.</t>
         </is>
       </c>
       <c r="P496" t="inlineStr"/>
@@ -17765,7 +17765,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>BCIO:015887</t>
+          <t>BCIO:015671</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -17777,7 +17777,7 @@
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr">
         <is>
-          <t>proportion monetary human income data item population statistic</t>
+          <t>percentage protective factor for harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="J497" t="inlineStr"/>
@@ -17785,7 +17785,7 @@
       <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr">
         <is>
-          <t>A(n) monetary human income data item population statistic that is the proportion of individuals having a monetary human income data item in the population.</t>
+          <t>A(n) protective factor for harmful behaviour population statistic that is the percentage value of protective factor for harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P497" t="inlineStr"/>
@@ -17800,7 +17800,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>BCIO:015884</t>
+          <t>BCIO:015672</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -17812,7 +17812,7 @@
       <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr">
         <is>
-          <t>maximum monetary human income data item population statistic</t>
+          <t>proportion protective factor for harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="J498" t="inlineStr"/>
@@ -17820,7 +17820,7 @@
       <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr">
         <is>
-          <t>A(n) monetary human income data item population statistic that is the maximum value of monetary human income data item in the population.</t>
+          <t>A(n) protective factor for harmful behaviour population statistic that is the proportion of individuals having a protective factor for harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P498" t="inlineStr"/>
@@ -17835,7 +17835,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>BCIO:015860</t>
+          <t>BCIO:015670</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
@@ -17847,7 +17847,7 @@
       <c r="H499" t="inlineStr"/>
       <c r="I499" t="inlineStr">
         <is>
-          <t>government assistance income data item population statistic</t>
+          <t>median protective factor for harmful behaviour population statistic</t>
         </is>
       </c>
       <c r="J499" t="inlineStr"/>
@@ -17855,7 +17855,7 @@
       <c r="L499" t="inlineStr"/>
       <c r="M499" t="inlineStr">
         <is>
-          <t>A population statistic about government assistance income data item.</t>
+          <t>A(n) protective factor for harmful behaviour population statistic that is the median value of protective factor for harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P499" t="inlineStr"/>
@@ -17870,7 +17870,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>BCIO:015861</t>
+          <t>BCIO:015667</t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -17880,17 +17880,17 @@
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
-      <c r="J500" t="inlineStr">
-        <is>
-          <t>mean government assistance income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>mean protective factor for harmful behaviour population statistic</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr"/>
       <c r="M500" t="inlineStr">
         <is>
-          <t>A(n) government assistance income data item population statistic that is the mean value of government assistance income data item in the population.</t>
+          <t>A(n) protective factor for harmful behaviour population statistic that is the mean value of protective factor for harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P500" t="inlineStr"/>
@@ -17905,7 +17905,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>BCIO:015865</t>
+          <t>BCIO:015668</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -17915,17 +17915,17 @@
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
-      <c r="I501" t="inlineStr"/>
-      <c r="J501" t="inlineStr">
-        <is>
-          <t>percentage government assistance income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>minimum protective factor for harmful behaviour population statistic</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr"/>
       <c r="M501" t="inlineStr">
         <is>
-          <t>A(n) government assistance income data item population statistic that is the percentage value of government assistance income data item in the population.</t>
+          <t>A(n) protective factor for harmful behaviour population statistic that is the minimum value of protective factor for harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P501" t="inlineStr"/>
@@ -17940,7 +17940,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>BCIO:015863</t>
+          <t>BCIO:015669</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -17950,17 +17950,17 @@
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr">
-        <is>
-          <t>maximum government assistance income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>maximum protective factor for harmful behaviour population statistic</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr"/>
       <c r="M502" t="inlineStr">
         <is>
-          <t>A(n) government assistance income data item population statistic that is the maximum value of government assistance income data item in the population.</t>
+          <t>A(n) protective factor for harmful behaviour population statistic that is the maximum value of protective factor for harmful behaviour in the population.</t>
         </is>
       </c>
       <c r="P502" t="inlineStr"/>
@@ -17975,7 +17975,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>BCIO:015864</t>
+          <t>BCIO:015270</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
@@ -17984,18 +17984,18 @@
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr"/>
-      <c r="H503" t="inlineStr"/>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>child population statistic</t>
+        </is>
+      </c>
       <c r="I503" t="inlineStr"/>
-      <c r="J503" t="inlineStr">
-        <is>
-          <t>median government assistance income data item population statistic</t>
-        </is>
-      </c>
+      <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr"/>
       <c r="M503" t="inlineStr">
         <is>
-          <t>A(n) government assistance income data item population statistic that is the median value of government assistance income data item in the population.</t>
+          <t>A population statistic about child.</t>
         </is>
       </c>
       <c r="P503" t="inlineStr"/>
@@ -18010,7 +18010,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>BCIO:015862</t>
+          <t>BCIO:015272</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -18020,17 +18020,17 @@
       <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr">
-        <is>
-          <t>minimum government assistance income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>proportion child population statistic</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr"/>
       <c r="M504" t="inlineStr">
         <is>
-          <t>A(n) government assistance income data item population statistic that is the minimum value of government assistance income data item in the population.</t>
+          <t>A(n) child population statistic that is the proportion of people that are a child in the population.</t>
         </is>
       </c>
       <c r="P504" t="inlineStr"/>
@@ -18045,7 +18045,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>BCIO:015866</t>
+          <t>BCIO:015271</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -18055,17 +18055,17 @@
       <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr"/>
-      <c r="I505" t="inlineStr"/>
-      <c r="J505" t="inlineStr">
-        <is>
-          <t>proportion government assistance income data item population statistic</t>
-        </is>
-      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>percentage child population statistic</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr"/>
       <c r="M505" t="inlineStr">
         <is>
-          <t>A(n) government assistance income data item population statistic that is the proportion of individuals having a government assistance income data item in the population.</t>
+          <t>A(n) child population statistic that is the percentage of people that are a child in the population.</t>
         </is>
       </c>
       <c r="P505" t="inlineStr"/>
@@ -18675,7 +18675,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>BCIO:015640</t>
+          <t>BCIO:015639</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -18687,7 +18687,7 @@
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="inlineStr">
         <is>
-          <t>median personal psychological attribute population statistic</t>
+          <t>maximum personal psychological attribute population statistic</t>
         </is>
       </c>
       <c r="J523" t="inlineStr"/>
@@ -18695,7 +18695,7 @@
       <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr">
         <is>
-          <t>A(n) personal psychological attribute population statistic that is the median value of personal psychological attribute in the population.</t>
+          <t>A(n) personal psychological attribute population statistic that is the maximum value of personal psychological attribute in the population.</t>
         </is>
       </c>
       <c r="P523" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>BCIO:015639</t>
+          <t>BCIO:015640</t>
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
@@ -18722,7 +18722,7 @@
       <c r="H524" t="inlineStr"/>
       <c r="I524" t="inlineStr">
         <is>
-          <t>maximum personal psychological attribute population statistic</t>
+          <t>median personal psychological attribute population statistic</t>
         </is>
       </c>
       <c r="J524" t="inlineStr"/>
@@ -18730,7 +18730,7 @@
       <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr">
         <is>
-          <t>A(n) personal psychological attribute population statistic that is the maximum value of personal psychological attribute in the population.</t>
+          <t>A(n) personal psychological attribute population statistic that is the median value of personal psychological attribute in the population.</t>
         </is>
       </c>
       <c r="P524" t="inlineStr"/>
@@ -22665,7 +22665,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>BCIO:015531</t>
+          <t>BCIO:015579</t>
         </is>
       </c>
       <c r="B637" t="inlineStr"/>
@@ -22678,14 +22678,14 @@
       <c r="I637" t="inlineStr"/>
       <c r="J637" t="inlineStr">
         <is>
-          <t>mother population statistic</t>
+          <t>percentage parent population statistic</t>
         </is>
       </c>
       <c r="K637" t="inlineStr"/>
       <c r="L637" t="inlineStr"/>
       <c r="M637" t="inlineStr">
         <is>
-          <t>A population statistic about mother.</t>
+          <t>A(n) parent population statistic that is the percentage of people that are a parent in the population.</t>
         </is>
       </c>
       <c r="P637" t="inlineStr"/>
@@ -22700,7 +22700,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>BCIO:015533</t>
+          <t>BCIO:015531</t>
         </is>
       </c>
       <c r="B638" t="inlineStr"/>
@@ -22711,16 +22711,16 @@
       <c r="G638" t="inlineStr"/>
       <c r="H638" t="inlineStr"/>
       <c r="I638" t="inlineStr"/>
-      <c r="J638" t="inlineStr"/>
-      <c r="K638" t="inlineStr">
-        <is>
-          <t>proportion mother population statistic</t>
-        </is>
-      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>mother population statistic</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr"/>
       <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr">
         <is>
-          <t>A(n) mother population statistic that is the proportion of people that are a mother in the population.</t>
+          <t>A population statistic about mother.</t>
         </is>
       </c>
       <c r="P638" t="inlineStr"/>
@@ -22735,7 +22735,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>BCIO:015532</t>
+          <t>BCIO:015533</t>
         </is>
       </c>
       <c r="B639" t="inlineStr"/>
@@ -22749,13 +22749,13 @@
       <c r="J639" t="inlineStr"/>
       <c r="K639" t="inlineStr">
         <is>
-          <t>percentage mother population statistic</t>
+          <t>proportion mother population statistic</t>
         </is>
       </c>
       <c r="L639" t="inlineStr"/>
       <c r="M639" t="inlineStr">
         <is>
-          <t>A(n) mother population statistic that is the percentage of people that are a mother in the population.</t>
+          <t>A(n) mother population statistic that is the proportion of people that are a mother in the population.</t>
         </is>
       </c>
       <c r="P639" t="inlineStr"/>
@@ -22770,7 +22770,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>BCIO:015207</t>
+          <t>BCIO:015532</t>
         </is>
       </c>
       <c r="B640" t="inlineStr"/>
@@ -22781,16 +22781,16 @@
       <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr"/>
       <c r="I640" t="inlineStr"/>
-      <c r="J640" t="inlineStr">
-        <is>
-          <t>adoptive parent population statistic</t>
-        </is>
-      </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>percentage mother population statistic</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr">
         <is>
-          <t>A population statistic about adoptive parent.</t>
+          <t>A(n) mother population statistic that is the percentage of people that are a mother in the population.</t>
         </is>
       </c>
       <c r="P640" t="inlineStr"/>
@@ -22805,7 +22805,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>BCIO:015209</t>
+          <t>BCIO:015207</t>
         </is>
       </c>
       <c r="B641" t="inlineStr"/>
@@ -22816,16 +22816,16 @@
       <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr"/>
       <c r="I641" t="inlineStr"/>
-      <c r="J641" t="inlineStr"/>
-      <c r="K641" t="inlineStr">
-        <is>
-          <t>proportion adoptive parent population statistic</t>
-        </is>
-      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>adoptive parent population statistic</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr"/>
       <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr">
         <is>
-          <t>A(n) adoptive parent population statistic that is the proportion of people that are a adoptive parent in the population.</t>
+          <t>A population statistic about adoptive parent.</t>
         </is>
       </c>
       <c r="P641" t="inlineStr"/>
@@ -22840,7 +22840,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>BCIO:015201</t>
+          <t>BCIO:015209</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
@@ -22854,13 +22854,13 @@
       <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr">
         <is>
-          <t>adoptive father population statistic</t>
+          <t>proportion adoptive parent population statistic</t>
         </is>
       </c>
       <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr">
         <is>
-          <t>A population statistic about adoptive father.</t>
+          <t>A(n) adoptive parent population statistic that is the proportion of people that are a adoptive parent in the population.</t>
         </is>
       </c>
       <c r="P642" t="inlineStr"/>
@@ -22875,7 +22875,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>BCIO:015202</t>
+          <t>BCIO:015201</t>
         </is>
       </c>
       <c r="B643" t="inlineStr"/>
@@ -22887,15 +22887,15 @@
       <c r="H643" t="inlineStr"/>
       <c r="I643" t="inlineStr"/>
       <c r="J643" t="inlineStr"/>
-      <c r="K643" t="inlineStr"/>
-      <c r="L643" t="inlineStr">
-        <is>
-          <t>percentage adoptive father population statistic</t>
-        </is>
-      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>adoptive father population statistic</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr">
         <is>
-          <t>A(n) adoptive father population statistic that is the percentage of people that are a adoptive father in the population.</t>
+          <t>A population statistic about adoptive father.</t>
         </is>
       </c>
       <c r="P643" t="inlineStr"/>
@@ -22910,7 +22910,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>BCIO:015203</t>
+          <t>BCIO:015202</t>
         </is>
       </c>
       <c r="B644" t="inlineStr"/>
@@ -22925,12 +22925,12 @@
       <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr">
         <is>
-          <t>proportion adoptive father population statistic</t>
+          <t>percentage adoptive father population statistic</t>
         </is>
       </c>
       <c r="M644" t="inlineStr">
         <is>
-          <t>A(n) adoptive father population statistic that is the proportion of people that are a adoptive father in the population.</t>
+          <t>A(n) adoptive father population statistic that is the percentage of people that are a adoptive father in the population.</t>
         </is>
       </c>
       <c r="P644" t="inlineStr"/>
@@ -22945,7 +22945,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>BCIO:015208</t>
+          <t>BCIO:015203</t>
         </is>
       </c>
       <c r="B645" t="inlineStr"/>
@@ -22957,15 +22957,15 @@
       <c r="H645" t="inlineStr"/>
       <c r="I645" t="inlineStr"/>
       <c r="J645" t="inlineStr"/>
-      <c r="K645" t="inlineStr">
-        <is>
-          <t>percentage adoptive parent population statistic</t>
-        </is>
-      </c>
-      <c r="L645" t="inlineStr"/>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>proportion adoptive father population statistic</t>
+        </is>
+      </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>A(n) adoptive parent population statistic that is the percentage of people that are a adoptive parent in the population.</t>
+          <t>A(n) adoptive father population statistic that is the proportion of people that are a adoptive father in the population.</t>
         </is>
       </c>
       <c r="P645" t="inlineStr"/>
@@ -22980,7 +22980,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>BCIO:015204</t>
+          <t>BCIO:015208</t>
         </is>
       </c>
       <c r="B646" t="inlineStr"/>
@@ -22994,13 +22994,13 @@
       <c r="J646" t="inlineStr"/>
       <c r="K646" t="inlineStr">
         <is>
-          <t>adoptive mother population statistic</t>
+          <t>percentage adoptive parent population statistic</t>
         </is>
       </c>
       <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr">
         <is>
-          <t>A population statistic about adoptive mother.</t>
+          <t>A(n) adoptive parent population statistic that is the percentage of people that are a adoptive parent in the population.</t>
         </is>
       </c>
       <c r="P646" t="inlineStr"/>
@@ -23015,7 +23015,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>BCIO:015205</t>
+          <t>BCIO:015204</t>
         </is>
       </c>
       <c r="B647" t="inlineStr"/>
@@ -23027,15 +23027,15 @@
       <c r="H647" t="inlineStr"/>
       <c r="I647" t="inlineStr"/>
       <c r="J647" t="inlineStr"/>
-      <c r="K647" t="inlineStr"/>
-      <c r="L647" t="inlineStr">
-        <is>
-          <t>percentage adoptive mother population statistic</t>
-        </is>
-      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>adoptive mother population statistic</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr">
         <is>
-          <t>A(n) adoptive mother population statistic that is the percentage of people that are a adoptive mother in the population.</t>
+          <t>A population statistic about adoptive mother.</t>
         </is>
       </c>
       <c r="P647" t="inlineStr"/>
@@ -23050,7 +23050,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>BCIO:015206</t>
+          <t>BCIO:015205</t>
         </is>
       </c>
       <c r="B648" t="inlineStr"/>
@@ -23065,12 +23065,12 @@
       <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr">
         <is>
-          <t>proportion adoptive mother population statistic</t>
+          <t>percentage adoptive mother population statistic</t>
         </is>
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>A(n) adoptive mother population statistic that is the proportion of people that are a adoptive mother in the population.</t>
+          <t>A(n) adoptive mother population statistic that is the percentage of people that are a adoptive mother in the population.</t>
         </is>
       </c>
       <c r="P648" t="inlineStr"/>
@@ -23085,7 +23085,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>BCIO:015324</t>
+          <t>BCIO:015206</t>
         </is>
       </c>
       <c r="B649" t="inlineStr"/>
@@ -23096,16 +23096,16 @@
       <c r="G649" t="inlineStr"/>
       <c r="H649" t="inlineStr"/>
       <c r="I649" t="inlineStr"/>
-      <c r="J649" t="inlineStr">
-        <is>
-          <t>father population statistic</t>
-        </is>
-      </c>
+      <c r="J649" t="inlineStr"/>
       <c r="K649" t="inlineStr"/>
-      <c r="L649" t="inlineStr"/>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>proportion adoptive mother population statistic</t>
+        </is>
+      </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>A population statistic about father.</t>
+          <t>A(n) adoptive mother population statistic that is the proportion of people that are a adoptive mother in the population.</t>
         </is>
       </c>
       <c r="P649" t="inlineStr"/>
@@ -23120,7 +23120,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>BCIO:015326</t>
+          <t>BCIO:015324</t>
         </is>
       </c>
       <c r="B650" t="inlineStr"/>
@@ -23131,16 +23131,16 @@
       <c r="G650" t="inlineStr"/>
       <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr"/>
-      <c r="J650" t="inlineStr"/>
-      <c r="K650" t="inlineStr">
-        <is>
-          <t>proportion father population statistic</t>
-        </is>
-      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>father population statistic</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr"/>
       <c r="L650" t="inlineStr"/>
       <c r="M650" t="inlineStr">
         <is>
-          <t>A(n) father population statistic that is the proportion of people that are a father in the population.</t>
+          <t>A population statistic about father.</t>
         </is>
       </c>
       <c r="P650" t="inlineStr"/>
@@ -23155,7 +23155,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>BCIO:015325</t>
+          <t>BCIO:015326</t>
         </is>
       </c>
       <c r="B651" t="inlineStr"/>
@@ -23169,13 +23169,13 @@
       <c r="J651" t="inlineStr"/>
       <c r="K651" t="inlineStr">
         <is>
-          <t>percentage father population statistic</t>
+          <t>proportion father population statistic</t>
         </is>
       </c>
       <c r="L651" t="inlineStr"/>
       <c r="M651" t="inlineStr">
         <is>
-          <t>A(n) father population statistic that is the percentage of people that are a father in the population.</t>
+          <t>A(n) father population statistic that is the proportion of people that are a father in the population.</t>
         </is>
       </c>
       <c r="P651" t="inlineStr"/>
@@ -23190,7 +23190,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>BCIO:015737</t>
+          <t>BCIO:015325</t>
         </is>
       </c>
       <c r="B652" t="inlineStr"/>
@@ -23201,16 +23201,16 @@
       <c r="G652" t="inlineStr"/>
       <c r="H652" t="inlineStr"/>
       <c r="I652" t="inlineStr"/>
-      <c r="J652" t="inlineStr">
-        <is>
-          <t>step-parent population statistic</t>
-        </is>
-      </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>percentage father population statistic</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
         <is>
-          <t>A population statistic about step-parent.</t>
+          <t>A(n) father population statistic that is the percentage of people that are a father in the population.</t>
         </is>
       </c>
       <c r="P652" t="inlineStr"/>
@@ -23225,7 +23225,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>BCIO:015738</t>
+          <t>BCIO:015737</t>
         </is>
       </c>
       <c r="B653" t="inlineStr"/>
@@ -23236,16 +23236,16 @@
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
       <c r="I653" t="inlineStr"/>
-      <c r="J653" t="inlineStr"/>
-      <c r="K653" t="inlineStr">
-        <is>
-          <t>percentage step-parent population statistic</t>
-        </is>
-      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>step-parent population statistic</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr">
         <is>
-          <t>A(n) step-parent population statistic that is the percentage of people that are a step-parent in the population.</t>
+          <t>A population statistic about step-parent.</t>
         </is>
       </c>
       <c r="P653" t="inlineStr"/>
@@ -23260,7 +23260,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>BCIO:015739</t>
+          <t>BCIO:015738</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -23274,13 +23274,13 @@
       <c r="J654" t="inlineStr"/>
       <c r="K654" t="inlineStr">
         <is>
-          <t>proportion step-parent population statistic</t>
+          <t>percentage step-parent population statistic</t>
         </is>
       </c>
       <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr">
         <is>
-          <t>A(n) step-parent population statistic that is the proportion of people that are a step-parent in the population.</t>
+          <t>A(n) step-parent population statistic that is the percentage of people that are a step-parent in the population.</t>
         </is>
       </c>
       <c r="P654" t="inlineStr"/>
@@ -23295,7 +23295,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>BCIO:015752</t>
+          <t>BCIO:015739</t>
         </is>
       </c>
       <c r="B655" t="inlineStr"/>
@@ -23309,13 +23309,13 @@
       <c r="J655" t="inlineStr"/>
       <c r="K655" t="inlineStr">
         <is>
-          <t>stepfather population statistic</t>
+          <t>proportion step-parent population statistic</t>
         </is>
       </c>
       <c r="L655" t="inlineStr"/>
       <c r="M655" t="inlineStr">
         <is>
-          <t>A population statistic about stepfather.</t>
+          <t>A(n) step-parent population statistic that is the proportion of people that are a step-parent in the population.</t>
         </is>
       </c>
       <c r="P655" t="inlineStr"/>
@@ -23330,7 +23330,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>BCIO:015753</t>
+          <t>BCIO:015752</t>
         </is>
       </c>
       <c r="B656" t="inlineStr"/>
@@ -23342,15 +23342,15 @@
       <c r="H656" t="inlineStr"/>
       <c r="I656" t="inlineStr"/>
       <c r="J656" t="inlineStr"/>
-      <c r="K656" t="inlineStr"/>
-      <c r="L656" t="inlineStr">
-        <is>
-          <t>percentage stepfather population statistic</t>
-        </is>
-      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>stepfather population statistic</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr"/>
       <c r="M656" t="inlineStr">
         <is>
-          <t>A(n) stepfather population statistic that is the percentage of people that are a stepfather in the population.</t>
+          <t>A population statistic about stepfather.</t>
         </is>
       </c>
       <c r="P656" t="inlineStr"/>
@@ -23365,7 +23365,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>BCIO:015754</t>
+          <t>BCIO:015753</t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -23380,12 +23380,12 @@
       <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr">
         <is>
-          <t>proportion stepfather population statistic</t>
+          <t>percentage stepfather population statistic</t>
         </is>
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>A(n) stepfather population statistic that is the proportion of people that are a stepfather in the population.</t>
+          <t>A(n) stepfather population statistic that is the percentage of people that are a stepfather in the population.</t>
         </is>
       </c>
       <c r="P657" t="inlineStr"/>
@@ -23400,7 +23400,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>BCIO:015755</t>
+          <t>BCIO:015754</t>
         </is>
       </c>
       <c r="B658" t="inlineStr"/>
@@ -23412,15 +23412,15 @@
       <c r="H658" t="inlineStr"/>
       <c r="I658" t="inlineStr"/>
       <c r="J658" t="inlineStr"/>
-      <c r="K658" t="inlineStr">
-        <is>
-          <t>stepmother population statistic</t>
-        </is>
-      </c>
-      <c r="L658" t="inlineStr"/>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>proportion stepfather population statistic</t>
+        </is>
+      </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>A population statistic about stepmother.</t>
+          <t>A(n) stepfather population statistic that is the proportion of people that are a stepfather in the population.</t>
         </is>
       </c>
       <c r="P658" t="inlineStr"/>
@@ -23435,7 +23435,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>BCIO:015757</t>
+          <t>BCIO:015755</t>
         </is>
       </c>
       <c r="B659" t="inlineStr"/>
@@ -23447,15 +23447,15 @@
       <c r="H659" t="inlineStr"/>
       <c r="I659" t="inlineStr"/>
       <c r="J659" t="inlineStr"/>
-      <c r="K659" t="inlineStr"/>
-      <c r="L659" t="inlineStr">
-        <is>
-          <t>proportion stepmother population statistic</t>
-        </is>
-      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>stepmother population statistic</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr"/>
       <c r="M659" t="inlineStr">
         <is>
-          <t>A(n) stepmother population statistic that is the proportion of people that are a stepmother in the population.</t>
+          <t>A population statistic about stepmother.</t>
         </is>
       </c>
       <c r="P659" t="inlineStr"/>
@@ -23470,7 +23470,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>BCIO:015756</t>
+          <t>BCIO:015757</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -23485,12 +23485,12 @@
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr">
         <is>
-          <t>percentage stepmother population statistic</t>
+          <t>proportion stepmother population statistic</t>
         </is>
       </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>A(n) stepmother population statistic that is the percentage of people that are a stepmother in the population.</t>
+          <t>A(n) stepmother population statistic that is the proportion of people that are a stepmother in the population.</t>
         </is>
       </c>
       <c r="P660" t="inlineStr"/>
@@ -23505,7 +23505,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>BCIO:015580</t>
+          <t>BCIO:015756</t>
         </is>
       </c>
       <c r="B661" t="inlineStr"/>
@@ -23516,16 +23516,16 @@
       <c r="G661" t="inlineStr"/>
       <c r="H661" t="inlineStr"/>
       <c r="I661" t="inlineStr"/>
-      <c r="J661" t="inlineStr">
-        <is>
-          <t>proportion parent population statistic</t>
-        </is>
-      </c>
+      <c r="J661" t="inlineStr"/>
       <c r="K661" t="inlineStr"/>
-      <c r="L661" t="inlineStr"/>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>percentage stepmother population statistic</t>
+        </is>
+      </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>A(n) parent population statistic that is the proportion of people that are a parent in the population.</t>
+          <t>A(n) stepmother population statistic that is the percentage of people that are a stepmother in the population.</t>
         </is>
       </c>
       <c r="P661" t="inlineStr"/>
@@ -23540,7 +23540,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>BCIO:015246</t>
+          <t>BCIO:015580</t>
         </is>
       </c>
       <c r="B662" t="inlineStr"/>
@@ -23553,14 +23553,14 @@
       <c r="I662" t="inlineStr"/>
       <c r="J662" t="inlineStr">
         <is>
-          <t>biological parent population statistic</t>
+          <t>proportion parent population statistic</t>
         </is>
       </c>
       <c r="K662" t="inlineStr"/>
       <c r="L662" t="inlineStr"/>
       <c r="M662" t="inlineStr">
         <is>
-          <t>A population statistic about biological parent.</t>
+          <t>A(n) parent population statistic that is the proportion of people that are a parent in the population.</t>
         </is>
       </c>
       <c r="P662" t="inlineStr"/>
@@ -23575,7 +23575,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>BCIO:015247</t>
+          <t>BCIO:015246</t>
         </is>
       </c>
       <c r="B663" t="inlineStr"/>
@@ -23586,16 +23586,16 @@
       <c r="G663" t="inlineStr"/>
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr"/>
-      <c r="J663" t="inlineStr"/>
-      <c r="K663" t="inlineStr">
-        <is>
-          <t>percentage biological parent population statistic</t>
-        </is>
-      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>biological parent population statistic</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr"/>
       <c r="L663" t="inlineStr"/>
       <c r="M663" t="inlineStr">
         <is>
-          <t>A(n) biological parent population statistic that is the percentage of people that are a biological parent in the population.</t>
+          <t>A population statistic about biological parent.</t>
         </is>
       </c>
       <c r="P663" t="inlineStr"/>
@@ -23610,7 +23610,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>BCIO:015243</t>
+          <t>BCIO:015247</t>
         </is>
       </c>
       <c r="B664" t="inlineStr"/>
@@ -23624,13 +23624,13 @@
       <c r="J664" t="inlineStr"/>
       <c r="K664" t="inlineStr">
         <is>
-          <t>biological mother population statistic</t>
+          <t>percentage biological parent population statistic</t>
         </is>
       </c>
       <c r="L664" t="inlineStr"/>
       <c r="M664" t="inlineStr">
         <is>
-          <t>A population statistic about biological mother.</t>
+          <t>A(n) biological parent population statistic that is the percentage of people that are a biological parent in the population.</t>
         </is>
       </c>
       <c r="P664" t="inlineStr"/>
@@ -23645,7 +23645,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>BCIO:015245</t>
+          <t>BCIO:015243</t>
         </is>
       </c>
       <c r="B665" t="inlineStr"/>
@@ -23657,15 +23657,15 @@
       <c r="H665" t="inlineStr"/>
       <c r="I665" t="inlineStr"/>
       <c r="J665" t="inlineStr"/>
-      <c r="K665" t="inlineStr"/>
-      <c r="L665" t="inlineStr">
-        <is>
-          <t>proportion biological mother population statistic</t>
-        </is>
-      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>biological mother population statistic</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr"/>
       <c r="M665" t="inlineStr">
         <is>
-          <t>A(n) biological mother population statistic that is the proportion of people that are a biological mother in the population.</t>
+          <t>A population statistic about biological mother.</t>
         </is>
       </c>
       <c r="P665" t="inlineStr"/>
@@ -23680,7 +23680,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>BCIO:015244</t>
+          <t>BCIO:015245</t>
         </is>
       </c>
       <c r="B666" t="inlineStr"/>
@@ -23695,12 +23695,12 @@
       <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr">
         <is>
-          <t>percentage biological mother population statistic</t>
+          <t>proportion biological mother population statistic</t>
         </is>
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>A(n) biological mother population statistic that is the percentage of people that are a biological mother in the population.</t>
+          <t>A(n) biological mother population statistic that is the proportion of people that are a biological mother in the population.</t>
         </is>
       </c>
       <c r="P666" t="inlineStr"/>
@@ -23715,7 +23715,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>BCIO:015240</t>
+          <t>BCIO:015244</t>
         </is>
       </c>
       <c r="B667" t="inlineStr"/>
@@ -23727,15 +23727,15 @@
       <c r="H667" t="inlineStr"/>
       <c r="I667" t="inlineStr"/>
       <c r="J667" t="inlineStr"/>
-      <c r="K667" t="inlineStr">
-        <is>
-          <t>biological father population statistic</t>
-        </is>
-      </c>
-      <c r="L667" t="inlineStr"/>
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>percentage biological mother population statistic</t>
+        </is>
+      </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>A population statistic about biological father.</t>
+          <t>A(n) biological mother population statistic that is the percentage of people that are a biological mother in the population.</t>
         </is>
       </c>
       <c r="P667" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>BCIO:015242</t>
+          <t>BCIO:015240</t>
         </is>
       </c>
       <c r="B668" t="inlineStr"/>
@@ -23762,15 +23762,15 @@
       <c r="H668" t="inlineStr"/>
       <c r="I668" t="inlineStr"/>
       <c r="J668" t="inlineStr"/>
-      <c r="K668" t="inlineStr"/>
-      <c r="L668" t="inlineStr">
-        <is>
-          <t>proportion biological father population statistic</t>
-        </is>
-      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>biological father population statistic</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr"/>
       <c r="M668" t="inlineStr">
         <is>
-          <t>A(n) biological father population statistic that is the proportion of people that are a biological father in the population.</t>
+          <t>A population statistic about biological father.</t>
         </is>
       </c>
       <c r="P668" t="inlineStr"/>
@@ -23785,7 +23785,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>BCIO:015241</t>
+          <t>BCIO:015242</t>
         </is>
       </c>
       <c r="B669" t="inlineStr"/>
@@ -23800,12 +23800,12 @@
       <c r="K669" t="inlineStr"/>
       <c r="L669" t="inlineStr">
         <is>
-          <t>percentage biological father population statistic</t>
+          <t>proportion biological father population statistic</t>
         </is>
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>A(n) biological father population statistic that is the percentage of people that are a biological father in the population.</t>
+          <t>A(n) biological father population statistic that is the proportion of people that are a biological father in the population.</t>
         </is>
       </c>
       <c r="P669" t="inlineStr"/>
@@ -23820,7 +23820,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>BCIO:015248</t>
+          <t>BCIO:015241</t>
         </is>
       </c>
       <c r="B670" t="inlineStr"/>
@@ -23832,15 +23832,15 @@
       <c r="H670" t="inlineStr"/>
       <c r="I670" t="inlineStr"/>
       <c r="J670" t="inlineStr"/>
-      <c r="K670" t="inlineStr">
-        <is>
-          <t>proportion biological parent population statistic</t>
-        </is>
-      </c>
-      <c r="L670" t="inlineStr"/>
+      <c r="K670" t="inlineStr"/>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>percentage biological father population statistic</t>
+        </is>
+      </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>A(n) biological parent population statistic that is the proportion of people that are a biological parent in the population.</t>
+          <t>A(n) biological father population statistic that is the percentage of people that are a biological father in the population.</t>
         </is>
       </c>
       <c r="P670" t="inlineStr"/>
@@ -23855,7 +23855,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>BCIO:015579</t>
+          <t>BCIO:015248</t>
         </is>
       </c>
       <c r="B671" t="inlineStr"/>
@@ -23866,16 +23866,16 @@
       <c r="G671" t="inlineStr"/>
       <c r="H671" t="inlineStr"/>
       <c r="I671" t="inlineStr"/>
-      <c r="J671" t="inlineStr">
-        <is>
-          <t>percentage parent population statistic</t>
-        </is>
-      </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>proportion biological parent population statistic</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr"/>
       <c r="M671" t="inlineStr">
         <is>
-          <t>A(n) parent population statistic that is the percentage of people that are a parent in the population.</t>
+          <t>A(n) biological parent population statistic that is the proportion of people that are a biological parent in the population.</t>
         </is>
       </c>
       <c r="P671" t="inlineStr"/>
@@ -24995,7 +24995,7 @@
       <c r="L703" t="inlineStr"/>
       <c r="M703" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25022,7 @@
       <c r="L704" t="inlineStr"/>
       <c r="M704" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -25411,7 +25411,7 @@
       <c r="F716" t="inlineStr"/>
       <c r="G716" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="H716" t="inlineStr"/>
@@ -27950,7 +27950,7 @@
       <c r="L786" t="inlineStr"/>
       <c r="M786" t="inlineStr">
         <is>
-          <t>A person who is between the ages of  13 and 19.</t>
+          <t>A person between 13 and 19 years of age.</t>
         </is>
       </c>
       <c r="P786" t="inlineStr"/>
@@ -28327,7 +28327,7 @@
       <c r="L796" t="inlineStr"/>
       <c r="M796" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -28342,7 +28342,7 @@
       <c r="D797" t="inlineStr"/>
       <c r="E797" t="inlineStr">
         <is>
-          <t>realizable</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="F797" t="inlineStr"/>
@@ -28438,7 +28438,7 @@
       <c r="L800" t="inlineStr"/>
       <c r="M800" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+          <t>b is a role means: b is a realizable entity and b exists because there is some single bearer that is in some special physical, social, or institutional set of circumstances in which this bearer does not have to beand b is not such that, if it ceases to exist, then the physical make-up of the bearer is thereby changed.</t>
         </is>
       </c>
       <c r="P800" t="inlineStr"/>
@@ -28453,7 +28453,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:015070</t>
         </is>
       </c>
       <c r="B801" t="inlineStr"/>
@@ -28463,7 +28463,7 @@
       <c r="F801" t="inlineStr"/>
       <c r="G801" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>interpersonal role</t>
         </is>
       </c>
       <c r="H801" t="inlineStr"/>
@@ -28473,7 +28473,7 @@
       <c r="L801" t="inlineStr"/>
       <c r="M801" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
         </is>
       </c>
       <c r="P801" t="inlineStr"/>
@@ -28482,13 +28482,17 @@
           <t>population</t>
         </is>
       </c>
-      <c r="R801" t="inlineStr"/>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>NCIT_C92454</t>
+        </is>
+      </c>
       <c r="S801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>BCIO:015084</t>
+          <t>BCIO:015108</t>
         </is>
       </c>
       <c r="B802" t="inlineStr"/>
@@ -28499,7 +28503,7 @@
       <c r="G802" t="inlineStr"/>
       <c r="H802" t="inlineStr">
         <is>
-          <t>preschool student role</t>
+          <t>parental role</t>
         </is>
       </c>
       <c r="I802" t="inlineStr"/>
@@ -28508,7 +28512,12 @@
       <c r="L802" t="inlineStr"/>
       <c r="M802" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
+          <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>A person can hold a parental role in a child's life without being that child's biological or legal parent.</t>
         </is>
       </c>
       <c r="P802" t="inlineStr"/>
@@ -28523,7 +28532,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>OBI:0000093</t>
         </is>
       </c>
       <c r="B803" t="inlineStr"/>
@@ -28531,19 +28540,19 @@
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr"/>
-      <c r="G803" t="inlineStr"/>
-      <c r="H803" t="inlineStr">
-        <is>
-          <t>school student role</t>
-        </is>
-      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>patient role</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr"/>
       <c r="I803" t="inlineStr"/>
       <c r="J803" t="inlineStr"/>
       <c r="K803" t="inlineStr"/>
       <c r="L803" t="inlineStr"/>
       <c r="M803" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
         </is>
       </c>
       <c r="P803" t="inlineStr"/>
@@ -28558,7 +28567,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:015080</t>
         </is>
       </c>
       <c r="B804" t="inlineStr"/>
@@ -28569,7 +28578,7 @@
       <c r="G804" t="inlineStr"/>
       <c r="H804" t="inlineStr">
         <is>
-          <t>trainee role</t>
+          <t>outpatient role</t>
         </is>
       </c>
       <c r="I804" t="inlineStr"/>
@@ -28578,7 +28587,7 @@
       <c r="L804" t="inlineStr"/>
       <c r="M804" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
         </is>
       </c>
       <c r="P804" t="inlineStr"/>
@@ -28593,7 +28602,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:015079</t>
         </is>
       </c>
       <c r="B805" t="inlineStr"/>
@@ -28604,7 +28613,7 @@
       <c r="G805" t="inlineStr"/>
       <c r="H805" t="inlineStr">
         <is>
-          <t>informal education student role</t>
+          <t>inpatient role</t>
         </is>
       </c>
       <c r="I805" t="inlineStr"/>
@@ -28613,7 +28622,7 @@
       <c r="L805" t="inlineStr"/>
       <c r="M805" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+          <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
         </is>
       </c>
       <c r="P805" t="inlineStr"/>
@@ -28628,7 +28637,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:015078</t>
         </is>
       </c>
       <c r="B806" t="inlineStr"/>
@@ -28636,19 +28645,19 @@
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="inlineStr"/>
-      <c r="G806" t="inlineStr"/>
-      <c r="H806" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>organisational role</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr"/>
       <c r="I806" t="inlineStr"/>
       <c r="J806" t="inlineStr"/>
       <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr"/>
       <c r="M806" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+          <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
         </is>
       </c>
       <c r="P806" t="inlineStr"/>
@@ -28660,14 +28669,14 @@
       <c r="R806" t="inlineStr"/>
       <c r="S806" t="inlineStr">
         <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+          <t>Scout leader, club chairperson</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:006081</t>
         </is>
       </c>
       <c r="B807" t="inlineStr"/>
@@ -28675,19 +28684,29 @@
       <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr"/>
       <c r="F807" t="inlineStr"/>
-      <c r="G807" t="inlineStr"/>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
       <c r="H807" t="inlineStr"/>
-      <c r="I807" t="inlineStr">
-        <is>
-          <t>doctoral student role</t>
-        </is>
-      </c>
+      <c r="I807" t="inlineStr"/>
       <c r="J807" t="inlineStr"/>
       <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr"/>
       <c r="M807" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
         </is>
       </c>
       <c r="P807" t="inlineStr"/>
@@ -28702,7 +28721,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B808" t="inlineStr"/>
@@ -28711,18 +28730,18 @@
       <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr"/>
       <c r="G808" t="inlineStr"/>
-      <c r="H808" t="inlineStr"/>
-      <c r="I808" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
-        </is>
-      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr"/>
       <c r="J808" t="inlineStr"/>
       <c r="K808" t="inlineStr"/>
       <c r="L808" t="inlineStr"/>
       <c r="M808" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="P808" t="inlineStr"/>
@@ -28737,7 +28756,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B809" t="inlineStr"/>
@@ -28749,7 +28768,7 @@
       <c r="H809" t="inlineStr"/>
       <c r="I809" t="inlineStr">
         <is>
-          <t>undergraduate student role</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="J809" t="inlineStr"/>
@@ -28757,7 +28776,7 @@
       <c r="L809" t="inlineStr"/>
       <c r="M809" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
       <c r="P809" t="inlineStr"/>
@@ -28767,12 +28786,16 @@
         </is>
       </c>
       <c r="R809" t="inlineStr"/>
-      <c r="S809" t="inlineStr"/>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B810" t="inlineStr"/>
@@ -28782,17 +28805,17 @@
       <c r="F810" t="inlineStr"/>
       <c r="G810" t="inlineStr"/>
       <c r="H810" t="inlineStr"/>
-      <c r="I810" t="inlineStr">
-        <is>
-          <t>masters student role</t>
-        </is>
-      </c>
-      <c r="J810" t="inlineStr"/>
+      <c r="I810" t="inlineStr"/>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>doctoral student role</t>
+        </is>
+      </c>
       <c r="K810" t="inlineStr"/>
       <c r="L810" t="inlineStr"/>
       <c r="M810" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="P810" t="inlineStr"/>
@@ -28807,7 +28830,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>BCIO:015070</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B811" t="inlineStr"/>
@@ -28815,19 +28838,19 @@
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr"/>
       <c r="F811" t="inlineStr"/>
-      <c r="G811" t="inlineStr">
-        <is>
-          <t>interpersonal role</t>
-        </is>
-      </c>
+      <c r="G811" t="inlineStr"/>
       <c r="H811" t="inlineStr"/>
       <c r="I811" t="inlineStr"/>
-      <c r="J811" t="inlineStr"/>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>graduate student role</t>
+        </is>
+      </c>
       <c r="K811" t="inlineStr"/>
       <c r="L811" t="inlineStr"/>
       <c r="M811" t="inlineStr">
         <is>
-          <t>A role relating to personal relationships or association between an individual and other individuals, including kinship relations, romantic, business, and social interactions.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
       <c r="P811" t="inlineStr"/>
@@ -28836,17 +28859,13 @@
           <t>population</t>
         </is>
       </c>
-      <c r="R811" t="inlineStr">
-        <is>
-          <t>NCIT_C92454</t>
-        </is>
-      </c>
+      <c r="R811" t="inlineStr"/>
       <c r="S811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>BCIO:015108</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B812" t="inlineStr"/>
@@ -28855,23 +28874,18 @@
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="inlineStr"/>
-      <c r="H812" t="inlineStr">
-        <is>
-          <t>parental role</t>
-        </is>
-      </c>
+      <c r="H812" t="inlineStr"/>
       <c r="I812" t="inlineStr"/>
-      <c r="J812" t="inlineStr"/>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
+        </is>
+      </c>
       <c r="K812" t="inlineStr"/>
       <c r="L812" t="inlineStr"/>
       <c r="M812" t="inlineStr">
         <is>
-          <t>An interpersonal role that is realised through a process of promoting and supporting the physical, emotional, social, and intellectual development of a child from infancy to adulthood.</t>
-        </is>
-      </c>
-      <c r="N812" t="inlineStr">
-        <is>
-          <t>A person can hold a parental role in a child's life without being that child's biological or legal parent.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="P812" t="inlineStr"/>
@@ -28886,7 +28900,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>OBI:0000093</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B813" t="inlineStr"/>
@@ -28894,19 +28908,19 @@
       <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
-      <c r="G813" t="inlineStr">
-        <is>
-          <t>patient role</t>
-        </is>
-      </c>
+      <c r="G813" t="inlineStr"/>
       <c r="H813" t="inlineStr"/>
       <c r="I813" t="inlineStr"/>
-      <c r="J813" t="inlineStr"/>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>masters student role</t>
+        </is>
+      </c>
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr"/>
       <c r="M813" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realized by being under the care of a physician or health care provider.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
       <c r="P813" t="inlineStr"/>
@@ -28921,7 +28935,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>BCIO:015080</t>
+          <t>BCIO:015084</t>
         </is>
       </c>
       <c r="B814" t="inlineStr"/>
@@ -28930,18 +28944,18 @@
       <c r="E814" t="inlineStr"/>
       <c r="F814" t="inlineStr"/>
       <c r="G814" t="inlineStr"/>
-      <c r="H814" t="inlineStr">
-        <is>
-          <t>outpatient role</t>
-        </is>
-      </c>
-      <c r="I814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>preschool student role</t>
+        </is>
+      </c>
       <c r="J814" t="inlineStr"/>
       <c r="K814" t="inlineStr"/>
       <c r="L814" t="inlineStr"/>
       <c r="M814" t="inlineStr">
         <is>
-          <t>A patient role which inheres in a person and is realized by coming to a healthcare facility for diagnosis or treatment but not being admitted for an overnight stay.</t>
+          <t>A student or trainee role realised by  currently learning at an initial level of organised instruction, primarily to familiarise the bearer to the school-type environment.</t>
         </is>
       </c>
       <c r="P814" t="inlineStr"/>
@@ -28956,7 +28970,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>BCIO:015079</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B815" t="inlineStr"/>
@@ -28965,18 +28979,18 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr"/>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>inpatient role</t>
-        </is>
-      </c>
-      <c r="I815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>school student role</t>
+        </is>
+      </c>
       <c r="J815" t="inlineStr"/>
       <c r="K815" t="inlineStr"/>
       <c r="L815" t="inlineStr"/>
       <c r="M815" t="inlineStr">
         <is>
-          <t>A patient role which inheres in a person and is realized by being under the care of a physician or health care provider and being admitted to a hospital or equivalent facility.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="P815" t="inlineStr"/>
@@ -28991,7 +29005,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>BCIO:015078</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B816" t="inlineStr"/>
@@ -28999,19 +29013,19 @@
       <c r="D816" t="inlineStr"/>
       <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr"/>
-      <c r="G816" t="inlineStr">
-        <is>
-          <t>organisational role</t>
-        </is>
-      </c>
+      <c r="G816" t="inlineStr"/>
       <c r="H816" t="inlineStr"/>
-      <c r="I816" t="inlineStr"/>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>trainee role</t>
+        </is>
+      </c>
       <c r="J816" t="inlineStr"/>
       <c r="K816" t="inlineStr"/>
       <c r="L816" t="inlineStr"/>
       <c r="M816" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by performing the activities deemed appropriate for that particular role as specified in the organisation rules.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="P816" t="inlineStr"/>
@@ -29021,16 +29035,12 @@
         </is>
       </c>
       <c r="R816" t="inlineStr"/>
-      <c r="S816" t="inlineStr">
-        <is>
-          <t>Scout leader, club chairperson</t>
-        </is>
-      </c>
+      <c r="S816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>BCIO:006081</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B817" t="inlineStr"/>
@@ -29038,29 +29048,19 @@
       <c r="D817" t="inlineStr"/>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>personal role</t>
-        </is>
-      </c>
+      <c r="G817" t="inlineStr"/>
       <c r="H817" t="inlineStr"/>
-      <c r="I817" t="inlineStr"/>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
+        </is>
+      </c>
       <c r="J817" t="inlineStr"/>
       <c r="K817" t="inlineStr"/>
       <c r="L817" t="inlineStr"/>
       <c r="M817" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
-        </is>
-      </c>
-      <c r="N817" t="inlineStr">
-        <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
-        </is>
-      </c>
-      <c r="O817" t="inlineStr">
-        <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="P817" t="inlineStr"/>
@@ -29228,19 +29228,19 @@
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr"/>
       <c r="F822" t="inlineStr"/>
-      <c r="G822" t="inlineStr">
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr">
         <is>
           <t>caregiving role</t>
         </is>
       </c>
-      <c r="H822" t="inlineStr"/>
       <c r="I822" t="inlineStr"/>
       <c r="J822" t="inlineStr"/>
       <c r="K822" t="inlineStr"/>
       <c r="L822" t="inlineStr"/>
       <c r="M822" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
+          <t>A personal role which inheres in a person and is realised by the person assuming responsibility for the physical and emotional needs of another who has difficulties with self care.</t>
         </is>
       </c>
       <c r="P822" t="inlineStr"/>
@@ -29493,7 +29493,7 @@
       <c r="L829" t="inlineStr"/>
       <c r="M829" t="inlineStr">
         <is>
-          <t>A disposition that inheres in some extended organism.</t>
+          <t>A &lt;disposition&gt; that inheres in some extended organism.</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
       <c r="L841" t="inlineStr"/>
       <c r="M841" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+          <t>A cognitive representation of themselves by a person or group.</t>
         </is>
       </c>
       <c r="P841" t="inlineStr"/>
@@ -30503,7 +30503,7 @@
       <c r="L856" t="inlineStr"/>
       <c r="M856" t="inlineStr">
         <is>
-          <t>A quality that inheres in some extended organism.</t>
+          <t>A bodily quality is a quality that inheres in some extended organism.</t>
         </is>
       </c>
       <c r="P856" t="inlineStr"/>
